--- a/output/quickfixwick_all_markets_daily.xlsx
+++ b/output/quickfixwick_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixwick daily (target = one tick beyond the entry bar's own wick (a short: below its low)), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-27); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-28 22:50 UTC.</t>
+          <t>quickfixwick daily (target = one tick beyond the entry bar's own wick (a short: below its low)), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-27); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-29 02:46 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfixwick_all_markets_daily.xlsx
+++ b/output/quickfixwick_all_markets_daily.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F2" t="n">
         <v>9</v>
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -639,7 +639,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -650,21 +650,21 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H4" t="n">
         <v>3</v>
       </c>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -675,19 +675,19 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>66.7</v>
+        <v>70</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>14.31</v>
+        <v>14.9</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>114307</v>
+        <v>114900.02</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>Dow_Futures_E_mini</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -698,20 +698,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -726,10 +726,10 @@
         <v>66.7</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>10.39</v>
+        <v>14.31</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>110387.91</v>
+        <v>114307</v>
       </c>
     </row>
     <row r="6">
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -986,11 +986,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -1034,11 +1034,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F12" t="n">
         <v>4</v>
@@ -1082,11 +1082,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -1130,11 +1130,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -1178,11 +1178,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F15" t="n">
         <v>2</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>50</v>
@@ -1226,11 +1226,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
@@ -1274,11 +1274,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
@@ -1322,11 +1322,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F18" t="n">
         <v>2</v>
@@ -1370,11 +1370,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1415,11 +1415,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1460,11 +1460,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1505,11 +1505,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1550,11 +1550,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1595,11 +1595,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1640,11 +1640,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F26" t="n">
         <v>2</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixwick daily (target = one tick beyond the entry bar's own wick (a short: below its low)), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-27); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-29 02:46 UTC.</t>
+          <t>quickfixwick daily (target = one tick beyond the entry bar's own wick (a short: below its low)), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-29); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-30 20:33 UTC.</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O88"/>
+  <dimension ref="A1:O90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5724,11 +5724,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -5737,45 +5737,28 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>1</v>
+          <t>2026-07-29</t>
+        </is>
       </c>
       <c r="G56" t="n">
-        <v>1360.4</v>
+        <v>2.69</v>
       </c>
       <c r="H56" t="n">
-        <v>1343.4</v>
+        <v>2.665</v>
       </c>
       <c r="I56" t="n">
-        <v>1406.1</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1406.1</v>
+        <v>2.756</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>target_bar</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>2.6882</v>
-      </c>
-      <c r="M56" s="2" t="n">
-        <v>2.6882</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N56" t="n">
-        <v>100000</v>
+        <v>100999.41</v>
       </c>
       <c r="O56" t="n">
-        <v>102688.24</v>
+        <v>100999.41</v>
       </c>
     </row>
     <row r="57">
@@ -5785,7 +5768,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -5794,28 +5777,28 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>1167</v>
+        <v>1360.4</v>
       </c>
       <c r="H57" t="n">
-        <v>1159.4</v>
+        <v>1343.4</v>
       </c>
       <c r="I57" t="n">
-        <v>1208.1</v>
+        <v>1406.1</v>
       </c>
       <c r="J57" t="n">
-        <v>1208.1</v>
+        <v>1406.1</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -5823,56 +5806,56 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>5.4079</v>
+        <v>2.6882</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>5.4079</v>
+        <v>2.6882</v>
       </c>
       <c r="N57" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O57" t="n">
         <v>102688.24</v>
-      </c>
-      <c r="O57" t="n">
-        <v>108241.51</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>2084.6</v>
+        <v>1167</v>
       </c>
       <c r="H58" t="n">
-        <v>2113.7</v>
+        <v>1159.4</v>
       </c>
       <c r="I58" t="n">
-        <v>2032.3</v>
+        <v>1208.1</v>
       </c>
       <c r="J58" t="n">
-        <v>2031.1</v>
+        <v>1208.1</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5880,16 +5863,16 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.8385</v>
+        <v>5.4079</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1.8385</v>
+        <v>5.4079</v>
       </c>
       <c r="N58" t="n">
-        <v>100000</v>
+        <v>102688.24</v>
       </c>
       <c r="O58" t="n">
-        <v>101838.49</v>
+        <v>108241.51</v>
       </c>
     </row>
     <row r="59">
@@ -5899,54 +5882,54 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>1641.5</v>
+        <v>2084.6</v>
       </c>
       <c r="H59" t="n">
-        <v>1621</v>
+        <v>2113.7</v>
       </c>
       <c r="I59" t="n">
-        <v>1682.7</v>
+        <v>2032.3</v>
       </c>
       <c r="J59" t="n">
-        <v>1621</v>
+        <v>2031.1</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M59" s="5" t="n">
-        <v>-1</v>
+        <v>1.8385</v>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>1.8385</v>
       </c>
       <c r="N59" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O59" t="n">
         <v>101838.49</v>
-      </c>
-      <c r="O59" t="n">
-        <v>100820.1</v>
       </c>
     </row>
     <row r="60">
@@ -5956,7 +5939,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -5965,45 +5948,45 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>1581.5</v>
+        <v>1641.5</v>
       </c>
       <c r="H60" t="n">
-        <v>1547.6</v>
+        <v>1621</v>
       </c>
       <c r="I60" t="n">
-        <v>1613.1</v>
+        <v>1682.7</v>
       </c>
       <c r="J60" t="n">
-        <v>1618.8</v>
+        <v>1621</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.1003</v>
-      </c>
-      <c r="M60" s="2" t="n">
-        <v>1.1003</v>
+        <v>-1</v>
+      </c>
+      <c r="M60" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N60" t="n">
+        <v>101838.49</v>
+      </c>
+      <c r="O60" t="n">
         <v>100820.1</v>
-      </c>
-      <c r="O60" t="n">
-        <v>101929.42</v>
       </c>
     </row>
     <row r="61">
@@ -6013,7 +5996,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6022,28 +6005,28 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>1559</v>
+        <v>1581.5</v>
       </c>
       <c r="H61" t="n">
-        <v>1539.5</v>
+        <v>1547.6</v>
       </c>
       <c r="I61" t="n">
-        <v>1619.6</v>
+        <v>1613.1</v>
       </c>
       <c r="J61" t="n">
-        <v>1619.6</v>
+        <v>1618.8</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -6051,79 +6034,79 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.1077</v>
+        <v>1.1003</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3.1077</v>
+        <v>1.1003</v>
       </c>
       <c r="N61" t="n">
+        <v>100820.1</v>
+      </c>
+      <c r="O61" t="n">
         <v>101929.42</v>
-      </c>
-      <c r="O61" t="n">
-        <v>105097.07</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>27907</v>
+        <v>1559</v>
       </c>
       <c r="H62" t="n">
-        <v>27965.76</v>
+        <v>1539.5</v>
       </c>
       <c r="I62" t="n">
-        <v>27612.99</v>
+        <v>1619.6</v>
       </c>
       <c r="J62" t="n">
-        <v>27965.76</v>
+        <v>1619.6</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M62" s="5" t="n">
-        <v>-1</v>
+        <v>3.1077</v>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>3.1077</v>
       </c>
       <c r="N62" t="n">
-        <v>100000</v>
+        <v>101929.42</v>
       </c>
       <c r="O62" t="n">
-        <v>99000</v>
+        <v>105097.07</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -6136,51 +6119,51 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>7206.55</v>
+        <v>27907</v>
       </c>
       <c r="H63" t="n">
-        <v>7223.26</v>
+        <v>27965.76</v>
       </c>
       <c r="I63" t="n">
-        <v>7146.24</v>
+        <v>27612.99</v>
       </c>
       <c r="J63" t="n">
-        <v>7146.24</v>
+        <v>27965.76</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.6092</v>
-      </c>
-      <c r="M63" s="2" t="n">
-        <v>3.6092</v>
+        <v>-1</v>
+      </c>
+      <c r="M63" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N63" t="n">
         <v>100000</v>
       </c>
       <c r="O63" t="n">
-        <v>103609.22</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -6193,28 +6176,28 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>6957.43</v>
+        <v>7206.55</v>
       </c>
       <c r="H64" t="n">
-        <v>6965.7</v>
+        <v>7223.26</v>
       </c>
       <c r="I64" t="n">
-        <v>6919.18</v>
+        <v>7146.24</v>
       </c>
       <c r="J64" t="n">
-        <v>6914.11</v>
+        <v>7146.24</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -6222,16 +6205,16 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>5.2382</v>
+        <v>3.6092</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>5.2382</v>
+        <v>3.6092</v>
       </c>
       <c r="N64" t="n">
         <v>100000</v>
       </c>
       <c r="O64" t="n">
-        <v>105238.21</v>
+        <v>103609.22</v>
       </c>
     </row>
     <row r="65">
@@ -6241,7 +6224,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -6250,45 +6233,45 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>6982.4</v>
+        <v>6957.43</v>
       </c>
       <c r="H65" t="n">
-        <v>6988.83</v>
+        <v>6965.7</v>
       </c>
       <c r="I65" t="n">
-        <v>6958.82</v>
+        <v>6919.18</v>
       </c>
       <c r="J65" t="n">
-        <v>7002</v>
+        <v>6914.11</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>-3.0482</v>
-      </c>
-      <c r="M65" s="5" t="n">
-        <v>-3.0482</v>
+        <v>5.2382</v>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>5.2382</v>
       </c>
       <c r="N65" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O65" t="n">
         <v>105238.21</v>
-      </c>
-      <c r="O65" t="n">
-        <v>102030.33</v>
       </c>
     </row>
     <row r="66">
@@ -6298,7 +6281,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -6307,42 +6290,45 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
         <v>6982.4</v>
       </c>
       <c r="H66" t="n">
-        <v>6992.85</v>
+        <v>6988.83</v>
       </c>
       <c r="I66" t="n">
-        <v>6870.79</v>
+        <v>6958.82</v>
+      </c>
+      <c r="J66" t="n">
+        <v>7002</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-1</v>
+        <v>-3.0482</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>-1</v>
+        <v>-3.0482</v>
       </c>
       <c r="N66" t="n">
+        <v>105238.21</v>
+      </c>
+      <c r="O66" t="n">
         <v>102030.33</v>
-      </c>
-      <c r="O66" t="n">
-        <v>101010.02</v>
       </c>
     </row>
     <row r="67">
@@ -6352,7 +6338,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -6361,25 +6347,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G67" t="n">
         <v>6982.4</v>
       </c>
       <c r="H67" t="n">
-        <v>6986.84</v>
+        <v>6992.85</v>
       </c>
       <c r="I67" t="n">
-        <v>6937.52</v>
+        <v>6870.79</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -6393,10 +6379,10 @@
         <v>-1</v>
       </c>
       <c r="N67" t="n">
+        <v>102030.33</v>
+      </c>
+      <c r="O67" t="n">
         <v>101010.02</v>
-      </c>
-      <c r="O67" t="n">
-        <v>99999.92</v>
       </c>
     </row>
     <row r="68">
@@ -6406,94 +6392,91 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>6794.4</v>
+        <v>6982.4</v>
       </c>
       <c r="H68" t="n">
-        <v>6770.77</v>
+        <v>6986.84</v>
       </c>
       <c r="I68" t="n">
-        <v>6870.44</v>
-      </c>
-      <c r="J68" t="n">
-        <v>6769.03</v>
+        <v>6937.52</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>-1.0736</v>
+        <v>-1</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>-1.0736</v>
+        <v>-1</v>
       </c>
       <c r="N68" t="n">
+        <v>101010.02</v>
+      </c>
+      <c r="O68" t="n">
         <v>99999.92</v>
-      </c>
-      <c r="O68" t="n">
-        <v>98926.28999999999</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F69" t="n">
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>86.081</v>
+        <v>6794.4</v>
       </c>
       <c r="H69" t="n">
-        <v>88.001</v>
+        <v>6770.77</v>
       </c>
       <c r="I69" t="n">
-        <v>83.669</v>
+        <v>6870.44</v>
       </c>
       <c r="J69" t="n">
-        <v>88.001</v>
+        <v>6769.03</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -6501,16 +6484,16 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>-1</v>
+        <v>-1.0736</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>-1</v>
+        <v>-1.0736</v>
       </c>
       <c r="N69" t="n">
-        <v>100000</v>
+        <v>99999.92</v>
       </c>
       <c r="O69" t="n">
-        <v>99000</v>
+        <v>98926.28999999999</v>
       </c>
     </row>
     <row r="70">
@@ -6520,94 +6503,94 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>73.84399999999999</v>
+        <v>86.081</v>
       </c>
       <c r="H70" t="n">
-        <v>71.999</v>
+        <v>88.001</v>
       </c>
       <c r="I70" t="n">
-        <v>76.301</v>
+        <v>83.669</v>
       </c>
       <c r="J70" t="n">
-        <v>76.301</v>
+        <v>88.001</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.3317</v>
-      </c>
-      <c r="M70" s="2" t="n">
-        <v>1.3317</v>
+        <v>-1</v>
+      </c>
+      <c r="M70" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N70" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O70" t="n">
         <v>99000</v>
-      </c>
-      <c r="O70" t="n">
-        <v>100318.39</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>15</v>
+        <v>73.84399999999999</v>
       </c>
       <c r="H71" t="n">
-        <v>15.26</v>
+        <v>71.999</v>
       </c>
       <c r="I71" t="n">
-        <v>14.83</v>
+        <v>76.301</v>
       </c>
       <c r="J71" t="n">
-        <v>14.83</v>
+        <v>76.301</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6615,22 +6598,22 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0.6538</v>
+        <v>1.3317</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>0.6538</v>
+        <v>1.3317</v>
       </c>
       <c r="N71" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O71" t="n">
-        <v>100653.85</v>
+        <v>100318.39</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -6643,51 +6626,51 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>20.89</v>
+        <v>15</v>
       </c>
       <c r="H72" t="n">
-        <v>21.07</v>
+        <v>15.26</v>
       </c>
       <c r="I72" t="n">
-        <v>20.76</v>
+        <v>14.83</v>
       </c>
       <c r="J72" t="n">
-        <v>21.08</v>
+        <v>14.83</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-1.0556</v>
-      </c>
-      <c r="M72" s="5" t="n">
-        <v>-1.0556</v>
+        <v>0.6538</v>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>0.6538</v>
       </c>
       <c r="N72" t="n">
         <v>100000</v>
       </c>
       <c r="O72" t="n">
-        <v>98944.44</v>
+        <v>100653.85</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Teucrium_Wheat_Fund</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -6700,28 +6683,28 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>0.8614000000000001</v>
+        <v>20.89</v>
       </c>
       <c r="H73" t="n">
-        <v>0.8637</v>
+        <v>21.07</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8577</v>
+        <v>20.76</v>
       </c>
       <c r="J73" t="n">
-        <v>0.8637</v>
+        <v>21.08</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -6729,16 +6712,16 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>-1</v>
+        <v>-1.0556</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>-1</v>
+        <v>-1.0556</v>
       </c>
       <c r="N73" t="n">
         <v>100000</v>
       </c>
       <c r="O73" t="n">
-        <v>99000</v>
+        <v>98944.44</v>
       </c>
     </row>
     <row r="74">
@@ -6748,7 +6731,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -6757,12 +6740,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -6772,30 +6755,30 @@
         <v>0.8614000000000001</v>
       </c>
       <c r="H74" t="n">
-        <v>0.8658</v>
+        <v>0.8637</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8602</v>
+        <v>0.8577</v>
       </c>
       <c r="J74" t="n">
-        <v>0.8602</v>
+        <v>0.8637</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0.2727</v>
-      </c>
-      <c r="M74" s="2" t="n">
-        <v>0.2727</v>
+        <v>-1</v>
+      </c>
+      <c r="M74" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N74" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O74" t="n">
         <v>99000</v>
-      </c>
-      <c r="O74" t="n">
-        <v>99270</v>
       </c>
     </row>
     <row r="75">
@@ -6805,111 +6788,111 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>0.8467</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H75" t="n">
-        <v>0.8436</v>
+        <v>0.8658</v>
       </c>
       <c r="I75" t="n">
-        <v>0.85</v>
+        <v>0.8602</v>
       </c>
       <c r="J75" t="n">
-        <v>0.8498</v>
+        <v>0.8602</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>data_end</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>0.2727</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1</v>
+        <v>0.2727</v>
       </c>
       <c r="N75" t="n">
+        <v>99000</v>
+      </c>
+      <c r="O75" t="n">
         <v>99270</v>
-      </c>
-      <c r="O75" t="n">
-        <v>100262.7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>116.5</v>
+        <v>0.8467</v>
       </c>
       <c r="H76" t="n">
-        <v>116.79</v>
+        <v>0.8436</v>
       </c>
       <c r="I76" t="n">
-        <v>115.7</v>
+        <v>0.85</v>
       </c>
       <c r="J76" t="n">
-        <v>116.79</v>
+        <v>0.8498</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>data_end</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M76" s="5" t="n">
-        <v>-1</v>
+        <v>1</v>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N76" t="n">
-        <v>100000</v>
+        <v>99270</v>
       </c>
       <c r="O76" t="n">
-        <v>99000</v>
+        <v>100262.7</v>
       </c>
     </row>
     <row r="77">
@@ -6919,7 +6902,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -6928,28 +6911,28 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>118.02</v>
+        <v>116.5</v>
       </c>
       <c r="H77" t="n">
-        <v>118.16</v>
+        <v>116.79</v>
       </c>
       <c r="I77" t="n">
-        <v>117.17</v>
+        <v>115.7</v>
       </c>
       <c r="J77" t="n">
-        <v>118.16</v>
+        <v>116.79</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6963,67 +6946,67 @@
         <v>-1</v>
       </c>
       <c r="N77" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O77" t="n">
         <v>99000</v>
-      </c>
-      <c r="O77" t="n">
-        <v>98010</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G78" t="n">
-        <v>97.81399999999999</v>
+        <v>118.02</v>
       </c>
       <c r="H78" t="n">
-        <v>97.569</v>
+        <v>118.16</v>
       </c>
       <c r="I78" t="n">
-        <v>98.10599999999999</v>
+        <v>117.17</v>
       </c>
       <c r="J78" t="n">
-        <v>98.10599999999999</v>
+        <v>118.16</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.1918</v>
-      </c>
-      <c r="M78" s="2" t="n">
-        <v>1.1918</v>
+        <v>-1</v>
+      </c>
+      <c r="M78" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N78" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O78" t="n">
-        <v>101191.84</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="79">
@@ -7033,7 +7016,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -7042,28 +7025,28 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>97.714</v>
+        <v>97.81399999999999</v>
       </c>
       <c r="H79" t="n">
-        <v>97.46899999999999</v>
+        <v>97.569</v>
       </c>
       <c r="I79" t="n">
-        <v>98.211</v>
+        <v>98.10599999999999</v>
       </c>
       <c r="J79" t="n">
-        <v>98.211</v>
+        <v>98.10599999999999</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -7071,16 +7054,16 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.0286</v>
+        <v>1.1918</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>2.0286</v>
+        <v>1.1918</v>
       </c>
       <c r="N79" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O79" t="n">
         <v>101191.84</v>
-      </c>
-      <c r="O79" t="n">
-        <v>103244.59</v>
       </c>
     </row>
     <row r="80">
@@ -7090,37 +7073,37 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" t="n">
-        <v>99.376</v>
+        <v>97.714</v>
       </c>
       <c r="H80" t="n">
-        <v>99.571</v>
+        <v>97.46899999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>98.874</v>
+        <v>98.211</v>
       </c>
       <c r="J80" t="n">
-        <v>98.874</v>
+        <v>98.211</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -7128,16 +7111,16 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.5744</v>
+        <v>2.0286</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2.5744</v>
+        <v>2.0286</v>
       </c>
       <c r="N80" t="n">
+        <v>101191.84</v>
+      </c>
+      <c r="O80" t="n">
         <v>103244.59</v>
-      </c>
-      <c r="O80" t="n">
-        <v>105902.47</v>
       </c>
     </row>
     <row r="81">
@@ -7147,7 +7130,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -7156,45 +7139,45 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>3</v>
       </c>
       <c r="G81" t="n">
-        <v>99.246</v>
+        <v>99.376</v>
       </c>
       <c r="H81" t="n">
-        <v>99.501</v>
+        <v>99.571</v>
       </c>
       <c r="I81" t="n">
-        <v>98.849</v>
+        <v>98.874</v>
       </c>
       <c r="J81" t="n">
-        <v>99.501</v>
+        <v>98.874</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M81" s="5" t="n">
-        <v>-1</v>
+        <v>2.5744</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>2.5744</v>
       </c>
       <c r="N81" t="n">
+        <v>103244.59</v>
+      </c>
+      <c r="O81" t="n">
         <v>105902.47</v>
-      </c>
-      <c r="O81" t="n">
-        <v>104843.45</v>
       </c>
     </row>
     <row r="82">
@@ -7204,7 +7187,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -7213,45 +7196,45 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G82" t="n">
-        <v>100.066</v>
+        <v>99.246</v>
       </c>
       <c r="H82" t="n">
-        <v>100.201</v>
+        <v>99.501</v>
       </c>
       <c r="I82" t="n">
-        <v>99.804</v>
+        <v>98.849</v>
       </c>
       <c r="J82" t="n">
-        <v>99.804</v>
+        <v>99.501</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.9407</v>
-      </c>
-      <c r="M82" s="2" t="n">
-        <v>1.9407</v>
+        <v>-1</v>
+      </c>
+      <c r="M82" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N82" t="n">
+        <v>105902.47</v>
+      </c>
+      <c r="O82" t="n">
         <v>104843.45</v>
-      </c>
-      <c r="O82" t="n">
-        <v>106878.19</v>
       </c>
     </row>
     <row r="83">
@@ -7261,7 +7244,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -7270,12 +7253,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -7285,13 +7268,13 @@
         <v>100.066</v>
       </c>
       <c r="H83" t="n">
-        <v>100.316</v>
+        <v>100.201</v>
       </c>
       <c r="I83" t="n">
-        <v>99.56399999999999</v>
+        <v>99.804</v>
       </c>
       <c r="J83" t="n">
-        <v>99.45999999999999</v>
+        <v>99.804</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -7299,16 +7282,16 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.424</v>
+        <v>1.9407</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2.424</v>
+        <v>1.9407</v>
       </c>
       <c r="N83" t="n">
+        <v>104843.45</v>
+      </c>
+      <c r="O83" t="n">
         <v>106878.19</v>
-      </c>
-      <c r="O83" t="n">
-        <v>109468.91</v>
       </c>
     </row>
     <row r="84">
@@ -7318,7 +7301,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -7327,12 +7310,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -7342,30 +7325,30 @@
         <v>100.066</v>
       </c>
       <c r="H84" t="n">
-        <v>100.361</v>
+        <v>100.316</v>
       </c>
       <c r="I84" t="n">
-        <v>99.249</v>
+        <v>99.56399999999999</v>
       </c>
       <c r="J84" t="n">
-        <v>100.361</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M84" s="5" t="n">
-        <v>-1</v>
+        <v>2.424</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>2.424</v>
       </c>
       <c r="N84" t="n">
+        <v>106878.19</v>
+      </c>
+      <c r="O84" t="n">
         <v>109468.91</v>
-      </c>
-      <c r="O84" t="n">
-        <v>108374.22</v>
       </c>
     </row>
     <row r="85">
@@ -7375,7 +7358,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -7384,28 +7367,28 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>100.621</v>
+        <v>100.066</v>
       </c>
       <c r="H85" t="n">
-        <v>100.911</v>
+        <v>100.361</v>
       </c>
       <c r="I85" t="n">
-        <v>100.489</v>
+        <v>99.249</v>
       </c>
       <c r="J85" t="n">
-        <v>100.911</v>
+        <v>100.361</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -7419,10 +7402,10 @@
         <v>-1</v>
       </c>
       <c r="N85" t="n">
+        <v>109468.91</v>
+      </c>
+      <c r="O85" t="n">
         <v>108374.22</v>
-      </c>
-      <c r="O85" t="n">
-        <v>107290.48</v>
       </c>
     </row>
     <row r="86">
@@ -7432,7 +7415,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -7441,55 +7424,55 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G86" t="n">
-        <v>101.411</v>
+        <v>100.621</v>
       </c>
       <c r="H86" t="n">
-        <v>101.526</v>
+        <v>100.911</v>
       </c>
       <c r="I86" t="n">
-        <v>101.079</v>
+        <v>100.489</v>
       </c>
       <c r="J86" t="n">
-        <v>101.079</v>
+        <v>100.911</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.887</v>
-      </c>
-      <c r="M86" s="2" t="n">
-        <v>2.887</v>
+        <v>-1</v>
+      </c>
+      <c r="M86" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N86" t="n">
+        <v>108374.22</v>
+      </c>
+      <c r="O86" t="n">
         <v>107290.48</v>
-      </c>
-      <c r="O86" t="n">
-        <v>110387.91</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -7498,28 +7481,28 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F87" t="n">
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>121.72</v>
+        <v>101.411</v>
       </c>
       <c r="H87" t="n">
-        <v>123.03</v>
+        <v>101.526</v>
       </c>
       <c r="I87" t="n">
-        <v>118.32</v>
+        <v>101.079</v>
       </c>
       <c r="J87" t="n">
-        <v>113.29</v>
+        <v>101.079</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -7527,72 +7510,186 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>6.4351</v>
+        <v>2.887</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>6.4351</v>
+        <v>2.887</v>
       </c>
       <c r="N87" t="n">
-        <v>100000</v>
+        <v>107290.48</v>
       </c>
       <c r="O87" t="n">
-        <v>106435.11</v>
+        <v>110387.91</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>10</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H88" t="n">
+        <v>101.491</v>
+      </c>
+      <c r="I88" t="n">
+        <v>101.084</v>
+      </c>
+      <c r="J88" t="n">
+        <v>101.084</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>target_bar</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>4.0875</v>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>4.0875</v>
+      </c>
+      <c r="N88" t="n">
+        <v>110387.91</v>
+      </c>
+      <c r="O88" t="n">
+        <v>114900.02</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>United_States_Oil_Fund_LP</t>
         </is>
       </c>
-      <c r="B88" t="n">
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" t="n">
+        <v>121.72</v>
+      </c>
+      <c r="H89" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="I89" t="n">
+        <v>118.32</v>
+      </c>
+      <c r="J89" t="n">
+        <v>113.29</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>target_bar</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>6.4351</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>6.4351</v>
+      </c>
+      <c r="N89" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O89" t="n">
+        <v>106435.11</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
         <v>2</v>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>short</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="F88" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" t="n">
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="n">
         <v>130.16</v>
       </c>
-      <c r="H88" t="n">
+      <c r="H90" t="n">
         <v>130.94</v>
       </c>
-      <c r="I88" t="n">
+      <c r="I90" t="n">
         <v>124.19</v>
       </c>
-      <c r="J88" t="n">
+      <c r="J90" t="n">
         <v>124.19</v>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t>target_bar</t>
         </is>
       </c>
-      <c r="L88" t="n">
+      <c r="L90" t="n">
         <v>7.6538</v>
       </c>
-      <c r="M88" s="2" t="n">
+      <c r="M90" s="2" t="n">
         <v>7.6538</v>
       </c>
-      <c r="N88" t="n">
+      <c r="N90" t="n">
         <v>106435.11</v>
       </c>
-      <c r="O88" t="n">
+      <c r="O90" t="n">
         <v>114581.49</v>
       </c>
     </row>

--- a/output/quickfixwick_all_markets_daily.xlsx
+++ b/output/quickfixwick_all_markets_daily.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F2" t="n">
         <v>9</v>
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -975,31 +975,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1011,43 +1011,43 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3.61</v>
+        <v>3.67</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>103609.22</v>
+        <v>103665.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>139</v>
+        <v>68</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1059,43 +1059,43 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2.6</v>
+        <v>3.61</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>102597.47</v>
+        <v>103609.22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>German_Long_Bund</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1107,19 +1107,19 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1.48</v>
+        <v>2.6</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>101478.26</v>
+        <v>102597.47</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures</t>
+          <t>German_Long_Bund</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -1130,11 +1130,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -1158,16 +1158,16 @@
         <v>100</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1.09</v>
+        <v>1.48</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>101094.59</v>
+        <v>101478.26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>Japanese_Yen_Futures</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -1178,20 +1178,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1200,16 +1200,16 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>100999.41</v>
+        <v>101094.59</v>
       </c>
     </row>
     <row r="16">
@@ -1226,11 +1226,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
@@ -1274,11 +1274,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
@@ -1322,11 +1322,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F18" t="n">
         <v>2</v>
@@ -1370,11 +1370,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1415,11 +1415,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1460,11 +1460,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1505,11 +1505,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1550,11 +1550,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1595,11 +1595,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1640,11 +1640,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F26" t="n">
         <v>2</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixwick daily (target = one tick beyond the entry bar's own wick (a short: below its low)), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-29); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-30 20:33 UTC.</t>
+          <t>quickfixwick daily (target = one tick beyond the entry bar's own wick (a short: below its low)), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-30); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-31 15:45 UTC.</t>
         </is>
       </c>
     </row>
@@ -5740,6 +5740,14 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
       <c r="G56" t="n">
         <v>2.69</v>
       </c>
@@ -5749,16 +5757,25 @@
       <c r="I56" t="n">
         <v>2.756</v>
       </c>
+      <c r="J56" t="n">
+        <v>2.756</v>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>target_bar</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>2.64</v>
       </c>
       <c r="N56" t="n">
         <v>100999.41</v>
       </c>
       <c r="O56" t="n">
-        <v>100999.41</v>
+        <v>103665.8</v>
       </c>
     </row>
     <row r="57">

--- a/output/quickfixwick_all_markets_daily.xlsx
+++ b/output/quickfixwick_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixwick daily (target = one tick beyond the entry bar's own wick (a short: below its low)), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-30); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-31 15:45 UTC.</t>
+          <t>quickfixwick daily (target = one tick beyond the entry bar's own wick (a short: below its low)), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-30); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-31 17:02 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfixwick_all_markets_daily.xlsx
+++ b/output/quickfixwick_all_markets_daily.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F2" t="n">
         <v>9</v>
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -986,11 +986,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
@@ -1034,11 +1034,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -1082,11 +1082,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
@@ -1130,11 +1130,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -1178,11 +1178,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -1226,11 +1226,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
@@ -1274,11 +1274,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
@@ -1322,11 +1322,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F18" t="n">
         <v>2</v>
@@ -1370,11 +1370,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1415,11 +1415,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1460,11 +1460,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1505,11 +1505,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1550,11 +1550,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1595,11 +1595,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1640,11 +1640,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F26" t="n">
         <v>2</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixwick daily (target = one tick beyond the entry bar's own wick (a short: below its low)), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-30); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-31 17:02 UTC.</t>
+          <t>quickfixwick daily (target = one tick beyond the entry bar's own wick (a short: below its low)), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-01 19:43 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfixwick_all_markets_daily.xlsx
+++ b/output/quickfixwick_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixwick daily (target = one tick beyond the entry bar's own wick (a short: below its low)), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-01 19:43 UTC.</t>
+          <t>quickfixwick daily (target = one tick beyond the entry bar's own wick (a short: below its low)), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-01 22:59 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfixwick_all_markets_daily.xlsx
+++ b/output/quickfixwick_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixwick daily (target = one tick beyond the entry bar's own wick (a short: below its low)), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-01 22:59 UTC.</t>
+          <t>quickfixwick daily (target = one tick beyond the entry bar's own wick (a short: below its low)), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-02 00:09 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfixwick_all_markets_daily.xlsx
+++ b/output/quickfixwick_all_markets_daily.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F2" t="n">
         <v>9</v>
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -986,11 +986,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
@@ -1034,11 +1034,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -1082,11 +1082,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
@@ -1130,11 +1130,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -1178,11 +1178,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -1226,11 +1226,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
@@ -1274,11 +1274,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
@@ -1322,11 +1322,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F18" t="n">
         <v>2</v>
@@ -1370,11 +1370,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1415,11 +1415,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1460,11 +1460,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1505,11 +1505,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1550,11 +1550,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1595,11 +1595,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1640,11 +1640,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F26" t="n">
         <v>2</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixwick daily (target = one tick beyond the entry bar's own wick (a short: below its low)), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-02 00:09 UTC.</t>
+          <t>quickfixwick daily (target = one tick beyond the entry bar's own wick (a short: below its low)), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-04); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-05 13:32 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfixwick_all_markets_daily.xlsx
+++ b/output/quickfixwick_all_markets_daily.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F2" t="n">
         <v>9</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>77.8</v>
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -960,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>75</v>
@@ -975,31 +975,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1011,43 +1011,43 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3.67</v>
+        <v>4.21</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>103665.8</v>
+        <v>104206.84</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1059,13 +1059,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3.61</v>
+        <v>3.67</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>103609.22</v>
+        <v>103665.8</v>
       </c>
     </row>
     <row r="13">
@@ -1082,11 +1082,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
@@ -1130,11 +1130,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -1178,11 +1178,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -1215,7 +1215,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -1226,20 +1226,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1251,43 +1251,43 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>0.65</v>
+        <v>0.98</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>100653.85</v>
+        <v>100978.03</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>151</v>
+        <v>73</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1299,34 +1299,34 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0.32</v>
+        <v>0.65</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>100318.39</v>
+        <v>100653.85</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EURO_Futures</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>71</v>
+        <v>153</v>
       </c>
       <c r="F18" t="n">
         <v>2</v>
@@ -1335,10 +1335,10 @@
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1350,16 +1350,16 @@
         <v>50</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>0.13</v>
+        <v>0.32</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>100133.48</v>
+        <v>100318.39</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CME_SOFR_Futures_3M</t>
+          <t>EURO_Futures</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1370,23 +1370,23 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1394,17 +1394,20 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="4" t="n">
-        <v>0</v>
+      <c r="L19" t="n">
+        <v>50</v>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>0.13</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>100000</v>
+        <v>100133.48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Global_X_Uranium_ETF</t>
+          <t>CME_SOFR_Futures_3M</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1415,11 +1418,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1449,7 +1452,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Japanese_10_Year_Bond_Futures</t>
+          <t>Global_X_Uranium_ETF</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1460,11 +1463,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1494,7 +1497,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NY_Crude_Oil_Futures</t>
+          <t>Japanese_10_Year_Bond_Futures</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1505,11 +1508,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1539,22 +1542,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Proshares_VIX_Short_Term_Futures_ETF</t>
+          <t>NY_Crude_Oil_Futures</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>143</v>
+        <v>73</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1584,22 +1587,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>US_10_Year_T_Note_Futures</t>
+          <t>Proshares_VIX_Short_Term_Futures_ETF</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1629,7 +1632,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>US_10_Year_T_Note_Futures</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1640,20 +1643,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1664,14 +1667,11 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="5" t="n">
-        <v>-1</v>
+      <c r="M25" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>99000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="26">
@@ -1688,11 +1688,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F26" t="n">
         <v>2</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixwick daily (target = one tick beyond the entry bar's own wick (a short: below its low)), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-04); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-05 13:32 UTC.</t>
+          <t>quickfixwick daily (target = one tick beyond the entry bar's own wick (a short: below its low)), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-06); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-07 13:34 UTC.</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O90"/>
+  <dimension ref="A1:O94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5100,11 +5100,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5113,51 +5113,34 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>2</v>
+          <t>2026-08-06</t>
+        </is>
       </c>
       <c r="G45" t="n">
-        <v>0.006417</v>
+        <v>4305.3</v>
       </c>
       <c r="H45" t="n">
-        <v>0.006454</v>
+        <v>4363.8</v>
       </c>
       <c r="I45" t="n">
-        <v>0.006377</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0.006377</v>
+        <v>4281.1</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>target_bar</t>
-        </is>
-      </c>
-      <c r="L45" t="n">
-        <v>1.0946</v>
-      </c>
-      <c r="M45" s="2" t="n">
-        <v>1.0946</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N45" t="n">
-        <v>100000</v>
+        <v>124218.4</v>
       </c>
       <c r="O45" t="n">
-        <v>101094.59</v>
+        <v>124218.4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>Japanese_Yen_Futures</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -5170,42 +5153,45 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" t="n">
-        <v>239.06</v>
+        <v>0.006417</v>
       </c>
       <c r="H46" t="n">
-        <v>239.73</v>
+        <v>0.006454</v>
       </c>
       <c r="I46" t="n">
-        <v>237.09</v>
+        <v>0.006377</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.006377</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M46" s="5" t="n">
-        <v>-1</v>
+        <v>1.0946</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>1.0946</v>
       </c>
       <c r="N46" t="n">
         <v>100000</v>
       </c>
       <c r="O46" t="n">
-        <v>99000</v>
+        <v>101094.59</v>
       </c>
     </row>
     <row r="47">
@@ -5215,7 +5201,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5224,45 +5210,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>251.58</v>
+        <v>239.06</v>
       </c>
       <c r="H47" t="n">
-        <v>251.91</v>
+        <v>239.73</v>
       </c>
       <c r="I47" t="n">
-        <v>249.56</v>
-      </c>
-      <c r="J47" t="n">
-        <v>249.56</v>
+        <v>237.09</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>6.1212</v>
-      </c>
-      <c r="M47" s="2" t="n">
-        <v>6.1212</v>
+        <v>-1</v>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N47" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O47" t="n">
         <v>99000</v>
-      </c>
-      <c r="O47" t="n">
-        <v>105060</v>
       </c>
     </row>
     <row r="48">
@@ -5272,7 +5255,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5281,28 +5264,28 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>255.38</v>
+        <v>251.58</v>
       </c>
       <c r="H48" t="n">
-        <v>256.63</v>
+        <v>251.91</v>
       </c>
       <c r="I48" t="n">
-        <v>252.74</v>
+        <v>249.56</v>
       </c>
       <c r="J48" t="n">
-        <v>252.74</v>
+        <v>249.56</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -5310,16 +5293,16 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.112</v>
+        <v>6.1212</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2.112</v>
+        <v>6.1212</v>
       </c>
       <c r="N48" t="n">
+        <v>99000</v>
+      </c>
+      <c r="O48" t="n">
         <v>105060</v>
-      </c>
-      <c r="O48" t="n">
-        <v>107278.87</v>
       </c>
     </row>
     <row r="49">
@@ -5329,64 +5312,64 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>235.2</v>
+        <v>255.38</v>
       </c>
       <c r="H49" t="n">
-        <v>234.36</v>
+        <v>256.63</v>
       </c>
       <c r="I49" t="n">
-        <v>238.51</v>
+        <v>252.74</v>
       </c>
       <c r="J49" t="n">
-        <v>234.36</v>
+        <v>252.74</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M49" s="5" t="n">
-        <v>-1</v>
+        <v>2.112</v>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>2.112</v>
       </c>
       <c r="N49" t="n">
+        <v>105060</v>
+      </c>
+      <c r="O49" t="n">
         <v>107278.87</v>
-      </c>
-      <c r="O49" t="n">
-        <v>106206.08</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5395,28 +5378,28 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>5.7714</v>
+        <v>235.2</v>
       </c>
       <c r="H50" t="n">
-        <v>5.6849</v>
+        <v>234.36</v>
       </c>
       <c r="I50" t="n">
-        <v>5.9641</v>
+        <v>238.51</v>
       </c>
       <c r="J50" t="n">
-        <v>5.6849</v>
+        <v>234.36</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -5430,10 +5413,10 @@
         <v>-1</v>
       </c>
       <c r="N50" t="n">
-        <v>100000</v>
+        <v>107278.87</v>
       </c>
       <c r="O50" t="n">
-        <v>99000</v>
+        <v>106206.08</v>
       </c>
     </row>
     <row r="51">
@@ -5443,7 +5426,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5452,12 +5435,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -5467,13 +5450,13 @@
         <v>5.7714</v>
       </c>
       <c r="H51" t="n">
-        <v>5.6774</v>
+        <v>5.6849</v>
       </c>
       <c r="I51" t="n">
-        <v>5.8491</v>
+        <v>5.9641</v>
       </c>
       <c r="J51" t="n">
-        <v>5.6774</v>
+        <v>5.6849</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -5487,10 +5470,10 @@
         <v>-1</v>
       </c>
       <c r="N51" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O51" t="n">
         <v>99000</v>
-      </c>
-      <c r="O51" t="n">
-        <v>98010</v>
       </c>
     </row>
     <row r="52">
@@ -5500,7 +5483,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5509,45 +5492,45 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>5.3133</v>
+        <v>5.7714</v>
       </c>
       <c r="H52" t="n">
-        <v>5.2459</v>
+        <v>5.6774</v>
       </c>
       <c r="I52" t="n">
-        <v>5.5851</v>
+        <v>5.8491</v>
       </c>
       <c r="J52" t="n">
-        <v>5.5851</v>
+        <v>5.6774</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>4.0326</v>
-      </c>
-      <c r="M52" s="2" t="n">
-        <v>4.0326</v>
+        <v>-1</v>
+      </c>
+      <c r="M52" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N52" t="n">
+        <v>99000</v>
+      </c>
+      <c r="O52" t="n">
         <v>98010</v>
-      </c>
-      <c r="O52" t="n">
-        <v>101962.39</v>
       </c>
     </row>
     <row r="53">
@@ -5557,37 +5540,37 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53" t="n">
-        <v>6.0956</v>
+        <v>5.3133</v>
       </c>
       <c r="H53" t="n">
-        <v>6.1481</v>
+        <v>5.2459</v>
       </c>
       <c r="I53" t="n">
-        <v>6.0629</v>
+        <v>5.5851</v>
       </c>
       <c r="J53" t="n">
-        <v>6.0629</v>
+        <v>5.5851</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -5595,26 +5578,26 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0.6229</v>
+        <v>4.0326</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>0.6229</v>
+        <v>4.0326</v>
       </c>
       <c r="N53" t="n">
+        <v>98010</v>
+      </c>
+      <c r="O53" t="n">
         <v>101962.39</v>
-      </c>
-      <c r="O53" t="n">
-        <v>102597.47</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -5623,45 +5606,45 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="F54" t="n">
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>3.305</v>
+        <v>6.0956</v>
       </c>
       <c r="H54" t="n">
-        <v>3.354</v>
+        <v>6.1481</v>
       </c>
       <c r="I54" t="n">
-        <v>3.217</v>
+        <v>6.0629</v>
       </c>
       <c r="J54" t="n">
-        <v>3.354</v>
+        <v>6.0629</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M54" s="5" t="n">
-        <v>-1</v>
+        <v>0.6229</v>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>0.6229</v>
       </c>
       <c r="N54" t="n">
-        <v>100000</v>
+        <v>101962.39</v>
       </c>
       <c r="O54" t="n">
-        <v>99000</v>
+        <v>102597.47</v>
       </c>
     </row>
     <row r="55">
@@ -5671,7 +5654,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -5680,12 +5663,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -5695,30 +5678,30 @@
         <v>3.305</v>
       </c>
       <c r="H55" t="n">
-        <v>3.356</v>
+        <v>3.354</v>
       </c>
       <c r="I55" t="n">
-        <v>3.202</v>
+        <v>3.217</v>
       </c>
       <c r="J55" t="n">
-        <v>3.202</v>
+        <v>3.354</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.0196</v>
-      </c>
-      <c r="M55" s="2" t="n">
-        <v>2.0196</v>
+        <v>-1</v>
+      </c>
+      <c r="M55" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N55" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O55" t="n">
         <v>99000</v>
-      </c>
-      <c r="O55" t="n">
-        <v>100999.41</v>
       </c>
     </row>
     <row r="56">
@@ -5728,37 +5711,37 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69</v>
+        <v>3.305</v>
       </c>
       <c r="H56" t="n">
-        <v>2.665</v>
+        <v>3.356</v>
       </c>
       <c r="I56" t="n">
-        <v>2.756</v>
+        <v>3.202</v>
       </c>
       <c r="J56" t="n">
-        <v>2.756</v>
+        <v>3.202</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -5766,26 +5749,26 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.64</v>
+        <v>2.0196</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2.64</v>
+        <v>2.0196</v>
       </c>
       <c r="N56" t="n">
+        <v>99000</v>
+      </c>
+      <c r="O56" t="n">
         <v>100999.41</v>
-      </c>
-      <c r="O56" t="n">
-        <v>103665.8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -5794,28 +5777,28 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>1360.4</v>
+        <v>2.69</v>
       </c>
       <c r="H57" t="n">
-        <v>1343.4</v>
+        <v>2.665</v>
       </c>
       <c r="I57" t="n">
-        <v>1406.1</v>
+        <v>2.756</v>
       </c>
       <c r="J57" t="n">
-        <v>1406.1</v>
+        <v>2.756</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -5823,16 +5806,16 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.6882</v>
+        <v>2.64</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2.6882</v>
+        <v>2.64</v>
       </c>
       <c r="N57" t="n">
-        <v>100000</v>
+        <v>100999.41</v>
       </c>
       <c r="O57" t="n">
-        <v>102688.24</v>
+        <v>103665.8</v>
       </c>
     </row>
     <row r="58">
@@ -5842,7 +5825,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -5851,28 +5834,28 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>1167</v>
+        <v>1360.4</v>
       </c>
       <c r="H58" t="n">
-        <v>1159.4</v>
+        <v>1343.4</v>
       </c>
       <c r="I58" t="n">
-        <v>1208.1</v>
+        <v>1406.1</v>
       </c>
       <c r="J58" t="n">
-        <v>1208.1</v>
+        <v>1406.1</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5880,56 +5863,56 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>5.4079</v>
+        <v>2.6882</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>5.4079</v>
+        <v>2.6882</v>
       </c>
       <c r="N58" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O58" t="n">
         <v>102688.24</v>
-      </c>
-      <c r="O58" t="n">
-        <v>108241.51</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>2084.6</v>
+        <v>1167</v>
       </c>
       <c r="H59" t="n">
-        <v>2113.7</v>
+        <v>1159.4</v>
       </c>
       <c r="I59" t="n">
-        <v>2032.3</v>
+        <v>1208.1</v>
       </c>
       <c r="J59" t="n">
-        <v>2031.1</v>
+        <v>1208.1</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5937,16 +5920,16 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.8385</v>
+        <v>5.4079</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1.8385</v>
+        <v>5.4079</v>
       </c>
       <c r="N59" t="n">
-        <v>100000</v>
+        <v>102688.24</v>
       </c>
       <c r="O59" t="n">
-        <v>101838.49</v>
+        <v>108241.51</v>
       </c>
     </row>
     <row r="60">
@@ -5956,54 +5939,54 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>1641.5</v>
+        <v>2084.6</v>
       </c>
       <c r="H60" t="n">
-        <v>1621</v>
+        <v>2113.7</v>
       </c>
       <c r="I60" t="n">
-        <v>1682.7</v>
+        <v>2032.3</v>
       </c>
       <c r="J60" t="n">
-        <v>1621</v>
+        <v>2031.1</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M60" s="5" t="n">
-        <v>-1</v>
+        <v>1.8385</v>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>1.8385</v>
       </c>
       <c r="N60" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O60" t="n">
         <v>101838.49</v>
-      </c>
-      <c r="O60" t="n">
-        <v>100820.1</v>
       </c>
     </row>
     <row r="61">
@@ -6013,7 +5996,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6022,45 +6005,45 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>1581.5</v>
+        <v>1641.5</v>
       </c>
       <c r="H61" t="n">
-        <v>1547.6</v>
+        <v>1621</v>
       </c>
       <c r="I61" t="n">
-        <v>1613.1</v>
+        <v>1682.7</v>
       </c>
       <c r="J61" t="n">
-        <v>1618.8</v>
+        <v>1621</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.1003</v>
-      </c>
-      <c r="M61" s="2" t="n">
-        <v>1.1003</v>
+        <v>-1</v>
+      </c>
+      <c r="M61" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N61" t="n">
+        <v>101838.49</v>
+      </c>
+      <c r="O61" t="n">
         <v>100820.1</v>
-      </c>
-      <c r="O61" t="n">
-        <v>101929.42</v>
       </c>
     </row>
     <row r="62">
@@ -6070,7 +6053,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6079,28 +6062,28 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>1559</v>
+        <v>1581.5</v>
       </c>
       <c r="H62" t="n">
-        <v>1539.5</v>
+        <v>1547.6</v>
       </c>
       <c r="I62" t="n">
-        <v>1619.6</v>
+        <v>1613.1</v>
       </c>
       <c r="J62" t="n">
-        <v>1619.6</v>
+        <v>1618.8</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -6108,83 +6091,83 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.1077</v>
+        <v>1.1003</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3.1077</v>
+        <v>1.1003</v>
       </c>
       <c r="N62" t="n">
+        <v>100820.1</v>
+      </c>
+      <c r="O62" t="n">
         <v>101929.42</v>
-      </c>
-      <c r="O62" t="n">
-        <v>105097.07</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>27907</v>
+        <v>1559</v>
       </c>
       <c r="H63" t="n">
-        <v>27965.76</v>
+        <v>1539.5</v>
       </c>
       <c r="I63" t="n">
-        <v>27612.99</v>
+        <v>1619.6</v>
       </c>
       <c r="J63" t="n">
-        <v>27965.76</v>
+        <v>1619.6</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M63" s="5" t="n">
-        <v>-1</v>
+        <v>3.1077</v>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>3.1077</v>
       </c>
       <c r="N63" t="n">
-        <v>100000</v>
+        <v>101929.42</v>
       </c>
       <c r="O63" t="n">
-        <v>99000</v>
+        <v>105097.07</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -6193,51 +6176,34 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>1</v>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="G64" t="n">
-        <v>7206.55</v>
+        <v>1769.6</v>
       </c>
       <c r="H64" t="n">
-        <v>7223.26</v>
+        <v>1798.4</v>
       </c>
       <c r="I64" t="n">
-        <v>7146.24</v>
-      </c>
-      <c r="J64" t="n">
-        <v>7146.24</v>
+        <v>1726.5</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>target_bar</t>
-        </is>
-      </c>
-      <c r="L64" t="n">
-        <v>3.6092</v>
-      </c>
-      <c r="M64" s="2" t="n">
-        <v>3.6092</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N64" t="n">
-        <v>100000</v>
+        <v>105097.07</v>
       </c>
       <c r="O64" t="n">
-        <v>103609.22</v>
+        <v>105097.07</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -6250,51 +6216,51 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>6957.43</v>
+        <v>27907</v>
       </c>
       <c r="H65" t="n">
-        <v>6965.7</v>
+        <v>27965.76</v>
       </c>
       <c r="I65" t="n">
-        <v>6919.18</v>
+        <v>27612.99</v>
       </c>
       <c r="J65" t="n">
-        <v>6914.11</v>
+        <v>27965.76</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>5.2382</v>
-      </c>
-      <c r="M65" s="2" t="n">
-        <v>5.2382</v>
+        <v>-1</v>
+      </c>
+      <c r="M65" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N65" t="n">
         <v>100000</v>
       </c>
       <c r="O65" t="n">
-        <v>105238.21</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -6307,55 +6273,55 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>6982.4</v>
+        <v>29892.8</v>
       </c>
       <c r="H66" t="n">
-        <v>6988.83</v>
+        <v>30074.01</v>
       </c>
       <c r="I66" t="n">
-        <v>6958.82</v>
+        <v>29530.74</v>
       </c>
       <c r="J66" t="n">
-        <v>7002</v>
+        <v>29530.74</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-3.0482</v>
-      </c>
-      <c r="M66" s="5" t="n">
-        <v>-3.0482</v>
+        <v>1.998</v>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>1.998</v>
       </c>
       <c r="N66" t="n">
-        <v>105238.21</v>
+        <v>99000</v>
       </c>
       <c r="O66" t="n">
-        <v>102030.33</v>
+        <v>100978.03</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -6364,52 +6330,55 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>6982.4</v>
+        <v>7206.55</v>
       </c>
       <c r="H67" t="n">
-        <v>6992.85</v>
+        <v>7223.26</v>
       </c>
       <c r="I67" t="n">
-        <v>6870.79</v>
+        <v>7146.24</v>
+      </c>
+      <c r="J67" t="n">
+        <v>7146.24</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M67" s="5" t="n">
-        <v>-1</v>
+        <v>3.6092</v>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>3.6092</v>
       </c>
       <c r="N67" t="n">
-        <v>102030.33</v>
+        <v>100000</v>
       </c>
       <c r="O67" t="n">
-        <v>101010.02</v>
+        <v>103609.22</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -6418,42 +6387,45 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>6982.4</v>
+        <v>7773</v>
       </c>
       <c r="H68" t="n">
-        <v>6986.84</v>
+        <v>7820.26</v>
       </c>
       <c r="I68" t="n">
-        <v>6937.52</v>
+        <v>7745.74</v>
+      </c>
+      <c r="J68" t="n">
+        <v>7745.74</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M68" s="5" t="n">
-        <v>-1</v>
+        <v>0.5768</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>0.5768</v>
       </c>
       <c r="N68" t="n">
-        <v>101010.02</v>
+        <v>103609.22</v>
       </c>
       <c r="O68" t="n">
-        <v>99999.92</v>
+        <v>104206.84</v>
       </c>
     </row>
     <row r="69">
@@ -6463,64 +6435,64 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="F69" t="n">
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>6794.4</v>
+        <v>6957.43</v>
       </c>
       <c r="H69" t="n">
-        <v>6770.77</v>
+        <v>6965.7</v>
       </c>
       <c r="I69" t="n">
-        <v>6870.44</v>
+        <v>6919.18</v>
       </c>
       <c r="J69" t="n">
-        <v>6769.03</v>
+        <v>6914.11</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>-1.0736</v>
-      </c>
-      <c r="M69" s="5" t="n">
-        <v>-1.0736</v>
+        <v>5.2382</v>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>5.2382</v>
       </c>
       <c r="N69" t="n">
-        <v>99999.92</v>
+        <v>100000</v>
       </c>
       <c r="O69" t="n">
-        <v>98926.28999999999</v>
+        <v>105238.21</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -6529,28 +6501,28 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>86.081</v>
+        <v>6982.4</v>
       </c>
       <c r="H70" t="n">
-        <v>88.001</v>
+        <v>6988.83</v>
       </c>
       <c r="I70" t="n">
-        <v>83.669</v>
+        <v>6958.82</v>
       </c>
       <c r="J70" t="n">
-        <v>88.001</v>
+        <v>7002</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -6558,83 +6530,80 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>-1</v>
+        <v>-3.0482</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>-1</v>
+        <v>-3.0482</v>
       </c>
       <c r="N70" t="n">
-        <v>100000</v>
+        <v>105238.21</v>
       </c>
       <c r="O70" t="n">
-        <v>99000</v>
+        <v>102030.33</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G71" t="n">
-        <v>73.84399999999999</v>
+        <v>6982.4</v>
       </c>
       <c r="H71" t="n">
-        <v>71.999</v>
+        <v>6992.85</v>
       </c>
       <c r="I71" t="n">
-        <v>76.301</v>
-      </c>
-      <c r="J71" t="n">
-        <v>76.301</v>
+        <v>6870.79</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.3317</v>
-      </c>
-      <c r="M71" s="2" t="n">
-        <v>1.3317</v>
+        <v>-1</v>
+      </c>
+      <c r="M71" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N71" t="n">
-        <v>99000</v>
+        <v>102030.33</v>
       </c>
       <c r="O71" t="n">
-        <v>100318.39</v>
+        <v>101010.02</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -6643,85 +6612,82 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>15</v>
+        <v>6982.4</v>
       </c>
       <c r="H72" t="n">
-        <v>15.26</v>
+        <v>6986.84</v>
       </c>
       <c r="I72" t="n">
-        <v>14.83</v>
-      </c>
-      <c r="J72" t="n">
-        <v>14.83</v>
+        <v>6937.52</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0.6538</v>
-      </c>
-      <c r="M72" s="2" t="n">
-        <v>0.6538</v>
+        <v>-1</v>
+      </c>
+      <c r="M72" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N72" t="n">
-        <v>100000</v>
+        <v>101010.02</v>
       </c>
       <c r="O72" t="n">
-        <v>100653.85</v>
+        <v>99999.92</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>20.89</v>
+        <v>6794.4</v>
       </c>
       <c r="H73" t="n">
-        <v>21.07</v>
+        <v>6770.77</v>
       </c>
       <c r="I73" t="n">
-        <v>20.76</v>
+        <v>6870.44</v>
       </c>
       <c r="J73" t="n">
-        <v>21.08</v>
+        <v>6769.03</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -6729,22 +6695,22 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>-1.0556</v>
+        <v>-1.0736</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>-1.0556</v>
+        <v>-1.0736</v>
       </c>
       <c r="N73" t="n">
-        <v>100000</v>
+        <v>99999.92</v>
       </c>
       <c r="O73" t="n">
-        <v>98944.44</v>
+        <v>98926.28999999999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -6757,28 +6723,28 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F74" t="n">
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>0.8614000000000001</v>
+        <v>86.081</v>
       </c>
       <c r="H74" t="n">
-        <v>0.8637</v>
+        <v>88.001</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8577</v>
+        <v>83.669</v>
       </c>
       <c r="J74" t="n">
-        <v>0.8637</v>
+        <v>88.001</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -6801,7 +6767,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -6809,33 +6775,33 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>0.8614000000000001</v>
+        <v>73.84399999999999</v>
       </c>
       <c r="H75" t="n">
-        <v>0.8658</v>
+        <v>71.999</v>
       </c>
       <c r="I75" t="n">
-        <v>0.8602</v>
+        <v>76.301</v>
       </c>
       <c r="J75" t="n">
-        <v>0.8602</v>
+        <v>76.301</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6843,79 +6809,79 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0.2727</v>
+        <v>1.3317</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>0.2727</v>
+        <v>1.3317</v>
       </c>
       <c r="N75" t="n">
         <v>99000</v>
       </c>
       <c r="O75" t="n">
-        <v>99270</v>
+        <v>100318.39</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>0.8467</v>
+        <v>15</v>
       </c>
       <c r="H76" t="n">
-        <v>0.8436</v>
+        <v>15.26</v>
       </c>
       <c r="I76" t="n">
-        <v>0.85</v>
+        <v>14.83</v>
       </c>
       <c r="J76" t="n">
-        <v>0.8498</v>
+        <v>14.83</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>data_end</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1</v>
+        <v>0.6538</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1</v>
+        <v>0.6538</v>
       </c>
       <c r="N76" t="n">
-        <v>99270</v>
+        <v>100000</v>
       </c>
       <c r="O76" t="n">
-        <v>100262.7</v>
+        <v>100653.85</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>Teucrium_Wheat_Fund</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -6928,28 +6894,28 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F77" t="n">
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>116.5</v>
+        <v>20.89</v>
       </c>
       <c r="H77" t="n">
-        <v>116.79</v>
+        <v>21.07</v>
       </c>
       <c r="I77" t="n">
-        <v>115.7</v>
+        <v>20.76</v>
       </c>
       <c r="J77" t="n">
-        <v>116.79</v>
+        <v>21.08</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6957,26 +6923,26 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>-1</v>
+        <v>-1.0556</v>
       </c>
       <c r="M77" s="5" t="n">
-        <v>-1</v>
+        <v>-1.0556</v>
       </c>
       <c r="N77" t="n">
         <v>100000</v>
       </c>
       <c r="O77" t="n">
-        <v>99000</v>
+        <v>98944.44</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -6985,28 +6951,28 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>118.02</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H78" t="n">
-        <v>118.16</v>
+        <v>0.8637</v>
       </c>
       <c r="I78" t="n">
-        <v>117.17</v>
+        <v>0.8577</v>
       </c>
       <c r="J78" t="n">
-        <v>118.16</v>
+        <v>0.8637</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -7020,50 +6986,50 @@
         <v>-1</v>
       </c>
       <c r="N78" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O78" t="n">
         <v>99000</v>
-      </c>
-      <c r="O78" t="n">
-        <v>98010</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>97.81399999999999</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H79" t="n">
-        <v>97.569</v>
+        <v>0.8658</v>
       </c>
       <c r="I79" t="n">
-        <v>98.10599999999999</v>
+        <v>0.8602</v>
       </c>
       <c r="J79" t="n">
-        <v>98.10599999999999</v>
+        <v>0.8602</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -7071,26 +7037,26 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.1918</v>
+        <v>0.2727</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1.1918</v>
+        <v>0.2727</v>
       </c>
       <c r="N79" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O79" t="n">
-        <v>101191.84</v>
+        <v>99270</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -7099,55 +7065,55 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>97.714</v>
+        <v>0.8467</v>
       </c>
       <c r="H80" t="n">
-        <v>97.46899999999999</v>
+        <v>0.8436</v>
       </c>
       <c r="I80" t="n">
-        <v>98.211</v>
+        <v>0.85</v>
       </c>
       <c r="J80" t="n">
-        <v>98.211</v>
+        <v>0.8498</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>data_end</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.0286</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2.0286</v>
+        <v>1</v>
       </c>
       <c r="N80" t="n">
-        <v>101191.84</v>
+        <v>99270</v>
       </c>
       <c r="O80" t="n">
-        <v>103244.59</v>
+        <v>100262.7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -7156,55 +7122,55 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>99.376</v>
+        <v>116.5</v>
       </c>
       <c r="H81" t="n">
-        <v>99.571</v>
+        <v>116.79</v>
       </c>
       <c r="I81" t="n">
-        <v>98.874</v>
+        <v>115.7</v>
       </c>
       <c r="J81" t="n">
-        <v>98.874</v>
+        <v>116.79</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.5744</v>
-      </c>
-      <c r="M81" s="2" t="n">
-        <v>2.5744</v>
+        <v>-1</v>
+      </c>
+      <c r="M81" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N81" t="n">
-        <v>103244.59</v>
+        <v>100000</v>
       </c>
       <c r="O81" t="n">
-        <v>105902.47</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -7213,28 +7179,28 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F82" t="n">
         <v>3</v>
       </c>
       <c r="G82" t="n">
-        <v>99.246</v>
+        <v>118.02</v>
       </c>
       <c r="H82" t="n">
-        <v>99.501</v>
+        <v>118.16</v>
       </c>
       <c r="I82" t="n">
-        <v>98.849</v>
+        <v>117.17</v>
       </c>
       <c r="J82" t="n">
-        <v>99.501</v>
+        <v>118.16</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -7248,10 +7214,10 @@
         <v>-1</v>
       </c>
       <c r="N82" t="n">
-        <v>105902.47</v>
+        <v>99000</v>
       </c>
       <c r="O82" t="n">
-        <v>104843.45</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="83">
@@ -7261,37 +7227,37 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F83" t="n">
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>100.066</v>
+        <v>97.81399999999999</v>
       </c>
       <c r="H83" t="n">
-        <v>100.201</v>
+        <v>97.569</v>
       </c>
       <c r="I83" t="n">
-        <v>99.804</v>
+        <v>98.10599999999999</v>
       </c>
       <c r="J83" t="n">
-        <v>99.804</v>
+        <v>98.10599999999999</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -7299,16 +7265,16 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.9407</v>
+        <v>1.1918</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1.9407</v>
+        <v>1.1918</v>
       </c>
       <c r="N83" t="n">
-        <v>104843.45</v>
+        <v>100000</v>
       </c>
       <c r="O83" t="n">
-        <v>106878.19</v>
+        <v>101191.84</v>
       </c>
     </row>
     <row r="84">
@@ -7318,37 +7284,37 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G84" t="n">
-        <v>100.066</v>
+        <v>97.714</v>
       </c>
       <c r="H84" t="n">
-        <v>100.316</v>
+        <v>97.46899999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>99.56399999999999</v>
+        <v>98.211</v>
       </c>
       <c r="J84" t="n">
-        <v>99.45999999999999</v>
+        <v>98.211</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -7356,16 +7322,16 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.424</v>
+        <v>2.0286</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2.424</v>
+        <v>2.0286</v>
       </c>
       <c r="N84" t="n">
-        <v>106878.19</v>
+        <v>101191.84</v>
       </c>
       <c r="O84" t="n">
-        <v>109468.91</v>
+        <v>103244.59</v>
       </c>
     </row>
     <row r="85">
@@ -7375,7 +7341,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -7384,45 +7350,45 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G85" t="n">
-        <v>100.066</v>
+        <v>99.376</v>
       </c>
       <c r="H85" t="n">
-        <v>100.361</v>
+        <v>99.571</v>
       </c>
       <c r="I85" t="n">
-        <v>99.249</v>
+        <v>98.874</v>
       </c>
       <c r="J85" t="n">
-        <v>100.361</v>
+        <v>98.874</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M85" s="5" t="n">
-        <v>-1</v>
+        <v>2.5744</v>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>2.5744</v>
       </c>
       <c r="N85" t="n">
-        <v>109468.91</v>
+        <v>103244.59</v>
       </c>
       <c r="O85" t="n">
-        <v>108374.22</v>
+        <v>105902.47</v>
       </c>
     </row>
     <row r="86">
@@ -7432,7 +7398,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -7441,28 +7407,28 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G86" t="n">
-        <v>100.621</v>
+        <v>99.246</v>
       </c>
       <c r="H86" t="n">
-        <v>100.911</v>
+        <v>99.501</v>
       </c>
       <c r="I86" t="n">
-        <v>100.489</v>
+        <v>98.849</v>
       </c>
       <c r="J86" t="n">
-        <v>100.911</v>
+        <v>99.501</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -7476,10 +7442,10 @@
         <v>-1</v>
       </c>
       <c r="N86" t="n">
-        <v>108374.22</v>
+        <v>105902.47</v>
       </c>
       <c r="O86" t="n">
-        <v>107290.48</v>
+        <v>104843.45</v>
       </c>
     </row>
     <row r="87">
@@ -7489,7 +7455,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -7498,28 +7464,28 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F87" t="n">
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>101.411</v>
+        <v>100.066</v>
       </c>
       <c r="H87" t="n">
-        <v>101.526</v>
+        <v>100.201</v>
       </c>
       <c r="I87" t="n">
-        <v>101.079</v>
+        <v>99.804</v>
       </c>
       <c r="J87" t="n">
-        <v>101.079</v>
+        <v>99.804</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -7527,16 +7493,16 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.887</v>
+        <v>1.9407</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2.887</v>
+        <v>1.9407</v>
       </c>
       <c r="N87" t="n">
-        <v>107290.48</v>
+        <v>104843.45</v>
       </c>
       <c r="O87" t="n">
-        <v>110387.91</v>
+        <v>106878.19</v>
       </c>
     </row>
     <row r="88">
@@ -7546,7 +7512,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -7555,28 +7521,28 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F88" t="n">
         <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>101.411</v>
+        <v>100.066</v>
       </c>
       <c r="H88" t="n">
-        <v>101.491</v>
+        <v>100.316</v>
       </c>
       <c r="I88" t="n">
-        <v>101.084</v>
+        <v>99.56399999999999</v>
       </c>
       <c r="J88" t="n">
-        <v>101.084</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -7584,26 +7550,26 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>4.0875</v>
+        <v>2.424</v>
       </c>
       <c r="M88" s="2" t="n">
-        <v>4.0875</v>
+        <v>2.424</v>
       </c>
       <c r="N88" t="n">
-        <v>110387.91</v>
+        <v>106878.19</v>
       </c>
       <c r="O88" t="n">
-        <v>114900.02</v>
+        <v>109468.91</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -7612,101 +7578,329 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F89" t="n">
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>121.72</v>
+        <v>100.066</v>
       </c>
       <c r="H89" t="n">
-        <v>123.03</v>
+        <v>100.361</v>
       </c>
       <c r="I89" t="n">
-        <v>118.32</v>
+        <v>99.249</v>
       </c>
       <c r="J89" t="n">
-        <v>113.29</v>
+        <v>100.361</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>6.4351</v>
-      </c>
-      <c r="M89" s="2" t="n">
-        <v>6.4351</v>
+        <v>-1</v>
+      </c>
+      <c r="M89" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N89" t="n">
-        <v>100000</v>
+        <v>109468.91</v>
       </c>
       <c r="O89" t="n">
-        <v>106435.11</v>
+        <v>108374.22</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>8</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>2</v>
+      </c>
+      <c r="G90" t="n">
+        <v>100.621</v>
+      </c>
+      <c r="H90" t="n">
+        <v>100.911</v>
+      </c>
+      <c r="I90" t="n">
+        <v>100.489</v>
+      </c>
+      <c r="J90" t="n">
+        <v>100.911</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M90" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N90" t="n">
+        <v>108374.22</v>
+      </c>
+      <c r="O90" t="n">
+        <v>107290.48</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>9</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H91" t="n">
+        <v>101.526</v>
+      </c>
+      <c r="I91" t="n">
+        <v>101.079</v>
+      </c>
+      <c r="J91" t="n">
+        <v>101.079</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>target_bar</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>2.887</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>2.887</v>
+      </c>
+      <c r="N91" t="n">
+        <v>107290.48</v>
+      </c>
+      <c r="O91" t="n">
+        <v>110387.91</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>10</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H92" t="n">
+        <v>101.491</v>
+      </c>
+      <c r="I92" t="n">
+        <v>101.084</v>
+      </c>
+      <c r="J92" t="n">
+        <v>101.084</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>target_bar</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>4.0875</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>4.0875</v>
+      </c>
+      <c r="N92" t="n">
+        <v>110387.91</v>
+      </c>
+      <c r="O92" t="n">
+        <v>114900.02</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
           <t>United_States_Oil_Fund_LP</t>
         </is>
       </c>
-      <c r="B90" t="n">
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" t="n">
+        <v>121.72</v>
+      </c>
+      <c r="H93" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="I93" t="n">
+        <v>118.32</v>
+      </c>
+      <c r="J93" t="n">
+        <v>113.29</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>target_bar</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>6.4351</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>6.4351</v>
+      </c>
+      <c r="N93" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O93" t="n">
+        <v>106435.11</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
         <v>2</v>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>short</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="F90" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" t="n">
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" t="n">
         <v>130.16</v>
       </c>
-      <c r="H90" t="n">
+      <c r="H94" t="n">
         <v>130.94</v>
       </c>
-      <c r="I90" t="n">
+      <c r="I94" t="n">
         <v>124.19</v>
       </c>
-      <c r="J90" t="n">
+      <c r="J94" t="n">
         <v>124.19</v>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="K94" t="inlineStr">
         <is>
           <t>target_bar</t>
         </is>
       </c>
-      <c r="L90" t="n">
+      <c r="L94" t="n">
         <v>7.6538</v>
       </c>
-      <c r="M90" s="2" t="n">
+      <c r="M94" s="2" t="n">
         <v>7.6538</v>
       </c>
-      <c r="N90" t="n">
+      <c r="N94" t="n">
         <v>106435.11</v>
       </c>
-      <c r="O90" t="n">
+      <c r="O94" t="n">
         <v>114581.49</v>
       </c>
     </row>

--- a/output/quickfixwick_all_markets_daily.xlsx
+++ b/output/quickfixwick_all_markets_daily.xlsx
@@ -543,82 +543,82 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>153</v>
+        <v>74</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>77.8</v>
+        <v>100</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>24.22</v>
+        <v>23.65</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>124218.4</v>
+        <v>123651.02</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>154</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -627,13 +627,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>23.65</v>
+        <v>22.98</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>123651.02</v>
+        <v>122976.22</v>
       </c>
     </row>
     <row r="4">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -864,7 +864,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>100</v>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -986,11 +986,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -1034,11 +1034,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F12" t="n">
         <v>3</v>
@@ -1082,11 +1082,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
@@ -1104,7 +1104,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>50</v>
@@ -1130,11 +1130,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -1178,11 +1178,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -1226,11 +1226,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F16" t="n">
         <v>2</v>
@@ -1274,11 +1274,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -1322,11 +1322,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F18" t="n">
         <v>2</v>
@@ -1370,11 +1370,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F19" t="n">
         <v>2</v>
@@ -1418,11 +1418,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1508,11 +1508,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1553,11 +1553,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1598,11 +1598,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1643,11 +1643,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F26" t="n">
         <v>2</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixwick daily (target = one tick beyond the entry bar's own wick (a short: below its low)), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-06); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-07 13:34 UTC.</t>
+          <t>quickfixwick daily (target = one tick beyond the entry bar's own wick (a short: below its low)), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-07); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-08 17:31 UTC.</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O94"/>
+  <dimension ref="A1:O96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5116,6 +5116,14 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
       <c r="G45" t="n">
         <v>4305.3</v>
       </c>
@@ -5125,16 +5133,25 @@
       <c r="I45" t="n">
         <v>4281.1</v>
       </c>
+      <c r="J45" t="n">
+        <v>4363.8</v>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N45" t="n">
         <v>124218.4</v>
       </c>
       <c r="O45" t="n">
-        <v>124218.4</v>
+        <v>122976.22</v>
       </c>
     </row>
     <row r="46">
@@ -5650,11 +5667,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -5663,45 +5680,28 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>1</v>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G55" t="n">
-        <v>3.305</v>
+        <v>6.7286</v>
       </c>
       <c r="H55" t="n">
-        <v>3.354</v>
+        <v>6.7656</v>
       </c>
       <c r="I55" t="n">
-        <v>3.217</v>
-      </c>
-      <c r="J55" t="n">
-        <v>3.354</v>
+        <v>6.5699</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M55" s="5" t="n">
-        <v>-1</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N55" t="n">
-        <v>100000</v>
+        <v>102597.47</v>
       </c>
       <c r="O55" t="n">
-        <v>99000</v>
+        <v>102597.47</v>
       </c>
     </row>
     <row r="56">
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -5720,12 +5720,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -5735,30 +5735,30 @@
         <v>3.305</v>
       </c>
       <c r="H56" t="n">
-        <v>3.356</v>
+        <v>3.354</v>
       </c>
       <c r="I56" t="n">
-        <v>3.202</v>
+        <v>3.217</v>
       </c>
       <c r="J56" t="n">
-        <v>3.202</v>
+        <v>3.354</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.0196</v>
-      </c>
-      <c r="M56" s="2" t="n">
-        <v>2.0196</v>
+        <v>-1</v>
+      </c>
+      <c r="M56" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N56" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O56" t="n">
         <v>99000</v>
-      </c>
-      <c r="O56" t="n">
-        <v>100999.41</v>
       </c>
     </row>
     <row r="57">
@@ -5768,37 +5768,37 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>2.69</v>
+        <v>3.305</v>
       </c>
       <c r="H57" t="n">
-        <v>2.665</v>
+        <v>3.356</v>
       </c>
       <c r="I57" t="n">
-        <v>2.756</v>
+        <v>3.202</v>
       </c>
       <c r="J57" t="n">
-        <v>2.756</v>
+        <v>3.202</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -5806,26 +5806,26 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.64</v>
+        <v>2.0196</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2.64</v>
+        <v>2.0196</v>
       </c>
       <c r="N57" t="n">
+        <v>99000</v>
+      </c>
+      <c r="O57" t="n">
         <v>100999.41</v>
-      </c>
-      <c r="O57" t="n">
-        <v>103665.8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -5834,28 +5834,28 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>1360.4</v>
+        <v>2.69</v>
       </c>
       <c r="H58" t="n">
-        <v>1343.4</v>
+        <v>2.665</v>
       </c>
       <c r="I58" t="n">
-        <v>1406.1</v>
+        <v>2.756</v>
       </c>
       <c r="J58" t="n">
-        <v>1406.1</v>
+        <v>2.756</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5863,16 +5863,16 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.6882</v>
+        <v>2.64</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2.6882</v>
+        <v>2.64</v>
       </c>
       <c r="N58" t="n">
-        <v>100000</v>
+        <v>100999.41</v>
       </c>
       <c r="O58" t="n">
-        <v>102688.24</v>
+        <v>103665.8</v>
       </c>
     </row>
     <row r="59">
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -5891,28 +5891,28 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>1167</v>
+        <v>1360.4</v>
       </c>
       <c r="H59" t="n">
-        <v>1159.4</v>
+        <v>1343.4</v>
       </c>
       <c r="I59" t="n">
-        <v>1208.1</v>
+        <v>1406.1</v>
       </c>
       <c r="J59" t="n">
-        <v>1208.1</v>
+        <v>1406.1</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5920,56 +5920,56 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>5.4079</v>
+        <v>2.6882</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5.4079</v>
+        <v>2.6882</v>
       </c>
       <c r="N59" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O59" t="n">
         <v>102688.24</v>
-      </c>
-      <c r="O59" t="n">
-        <v>108241.51</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>2084.6</v>
+        <v>1167</v>
       </c>
       <c r="H60" t="n">
-        <v>2113.7</v>
+        <v>1159.4</v>
       </c>
       <c r="I60" t="n">
-        <v>2032.3</v>
+        <v>1208.1</v>
       </c>
       <c r="J60" t="n">
-        <v>2031.1</v>
+        <v>1208.1</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5977,73 +5977,56 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.8385</v>
+        <v>5.4079</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1.8385</v>
+        <v>5.4079</v>
       </c>
       <c r="N60" t="n">
-        <v>100000</v>
+        <v>102688.24</v>
       </c>
       <c r="O60" t="n">
-        <v>101838.49</v>
+        <v>108241.51</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>1</v>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G61" t="n">
-        <v>1641.5</v>
+        <v>1386.6</v>
       </c>
       <c r="H61" t="n">
-        <v>1621</v>
+        <v>1412.1</v>
       </c>
       <c r="I61" t="n">
-        <v>1682.7</v>
-      </c>
-      <c r="J61" t="n">
-        <v>1621</v>
+        <v>1365.4</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="L61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M61" s="5" t="n">
-        <v>-1</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N61" t="n">
-        <v>101838.49</v>
+        <v>108241.51</v>
       </c>
       <c r="O61" t="n">
-        <v>100820.1</v>
+        <v>108241.51</v>
       </c>
     </row>
     <row r="62">
@@ -6053,37 +6036,37 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>1581.5</v>
+        <v>2084.6</v>
       </c>
       <c r="H62" t="n">
-        <v>1547.6</v>
+        <v>2113.7</v>
       </c>
       <c r="I62" t="n">
-        <v>1613.1</v>
+        <v>2032.3</v>
       </c>
       <c r="J62" t="n">
-        <v>1618.8</v>
+        <v>2031.1</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -6091,16 +6074,16 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.1003</v>
+        <v>1.8385</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1.1003</v>
+        <v>1.8385</v>
       </c>
       <c r="N62" t="n">
-        <v>100820.1</v>
+        <v>100000</v>
       </c>
       <c r="O62" t="n">
-        <v>101929.42</v>
+        <v>101838.49</v>
       </c>
     </row>
     <row r="63">
@@ -6110,7 +6093,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6119,45 +6102,45 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>1559</v>
+        <v>1641.5</v>
       </c>
       <c r="H63" t="n">
-        <v>1539.5</v>
+        <v>1621</v>
       </c>
       <c r="I63" t="n">
-        <v>1619.6</v>
+        <v>1682.7</v>
       </c>
       <c r="J63" t="n">
-        <v>1619.6</v>
+        <v>1621</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.1077</v>
-      </c>
-      <c r="M63" s="2" t="n">
-        <v>3.1077</v>
+        <v>-1</v>
+      </c>
+      <c r="M63" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N63" t="n">
-        <v>101929.42</v>
+        <v>101838.49</v>
       </c>
       <c r="O63" t="n">
-        <v>105097.07</v>
+        <v>100820.1</v>
       </c>
     </row>
     <row r="64">
@@ -6167,104 +6150,121 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>1769.6</v>
+        <v>1581.5</v>
       </c>
       <c r="H64" t="n">
-        <v>1798.4</v>
+        <v>1547.6</v>
       </c>
       <c r="I64" t="n">
-        <v>1726.5</v>
+        <v>1613.1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1618.8</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>target_bar</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>1.1003</v>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>1.1003</v>
       </c>
       <c r="N64" t="n">
-        <v>105097.07</v>
+        <v>100820.1</v>
       </c>
       <c r="O64" t="n">
-        <v>105097.07</v>
+        <v>101929.42</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>27907</v>
+        <v>1559</v>
       </c>
       <c r="H65" t="n">
-        <v>27965.76</v>
+        <v>1539.5</v>
       </c>
       <c r="I65" t="n">
-        <v>27612.99</v>
+        <v>1619.6</v>
       </c>
       <c r="J65" t="n">
-        <v>27965.76</v>
+        <v>1619.6</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M65" s="5" t="n">
-        <v>-1</v>
+        <v>3.1077</v>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>3.1077</v>
       </c>
       <c r="N65" t="n">
-        <v>100000</v>
+        <v>101929.42</v>
       </c>
       <c r="O65" t="n">
-        <v>99000</v>
+        <v>105097.07</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -6276,48 +6276,31 @@
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>1</v>
-      </c>
       <c r="G66" t="n">
-        <v>29892.8</v>
+        <v>1769.6</v>
       </c>
       <c r="H66" t="n">
-        <v>30074.01</v>
+        <v>1798.4</v>
       </c>
       <c r="I66" t="n">
-        <v>29530.74</v>
-      </c>
-      <c r="J66" t="n">
-        <v>29530.74</v>
+        <v>1726.5</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>target_bar</t>
-        </is>
-      </c>
-      <c r="L66" t="n">
-        <v>1.998</v>
-      </c>
-      <c r="M66" s="2" t="n">
-        <v>1.998</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N66" t="n">
-        <v>99000</v>
+        <v>105097.07</v>
       </c>
       <c r="O66" t="n">
-        <v>100978.03</v>
+        <v>105097.07</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -6330,51 +6313,51 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>7206.55</v>
+        <v>27907</v>
       </c>
       <c r="H67" t="n">
-        <v>7223.26</v>
+        <v>27965.76</v>
       </c>
       <c r="I67" t="n">
-        <v>7146.24</v>
+        <v>27612.99</v>
       </c>
       <c r="J67" t="n">
-        <v>7146.24</v>
+        <v>27965.76</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3.6092</v>
-      </c>
-      <c r="M67" s="2" t="n">
-        <v>3.6092</v>
+        <v>-1</v>
+      </c>
+      <c r="M67" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N67" t="n">
         <v>100000</v>
       </c>
       <c r="O67" t="n">
-        <v>103609.22</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -6399,16 +6382,16 @@
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>7773</v>
+        <v>29892.8</v>
       </c>
       <c r="H68" t="n">
-        <v>7820.26</v>
+        <v>30074.01</v>
       </c>
       <c r="I68" t="n">
-        <v>7745.74</v>
+        <v>29530.74</v>
       </c>
       <c r="J68" t="n">
-        <v>7745.74</v>
+        <v>29530.74</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -6416,22 +6399,22 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0.5768</v>
+        <v>1.998</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>0.5768</v>
+        <v>1.998</v>
       </c>
       <c r="N68" t="n">
-        <v>103609.22</v>
+        <v>99000</v>
       </c>
       <c r="O68" t="n">
-        <v>104206.84</v>
+        <v>100978.03</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -6444,28 +6427,28 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F69" t="n">
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>6957.43</v>
+        <v>7206.55</v>
       </c>
       <c r="H69" t="n">
-        <v>6965.7</v>
+        <v>7223.26</v>
       </c>
       <c r="I69" t="n">
-        <v>6919.18</v>
+        <v>7146.24</v>
       </c>
       <c r="J69" t="n">
-        <v>6914.11</v>
+        <v>7146.24</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -6473,22 +6456,22 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>5.2382</v>
+        <v>3.6092</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>5.2382</v>
+        <v>3.6092</v>
       </c>
       <c r="N69" t="n">
         <v>100000</v>
       </c>
       <c r="O69" t="n">
-        <v>105238.21</v>
+        <v>103609.22</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -6501,45 +6484,45 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>6982.4</v>
+        <v>7773</v>
       </c>
       <c r="H70" t="n">
-        <v>6988.83</v>
+        <v>7820.26</v>
       </c>
       <c r="I70" t="n">
-        <v>6958.82</v>
+        <v>7745.74</v>
       </c>
       <c r="J70" t="n">
-        <v>7002</v>
+        <v>7745.74</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>-3.0482</v>
-      </c>
-      <c r="M70" s="5" t="n">
-        <v>-3.0482</v>
+        <v>0.5768</v>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>0.5768</v>
       </c>
       <c r="N70" t="n">
-        <v>105238.21</v>
+        <v>103609.22</v>
       </c>
       <c r="O70" t="n">
-        <v>102030.33</v>
+        <v>104206.84</v>
       </c>
     </row>
     <row r="71">
@@ -6549,7 +6532,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -6558,42 +6541,45 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>6982.4</v>
+        <v>6957.43</v>
       </c>
       <c r="H71" t="n">
-        <v>6992.85</v>
+        <v>6965.7</v>
       </c>
       <c r="I71" t="n">
-        <v>6870.79</v>
+        <v>6919.18</v>
+      </c>
+      <c r="J71" t="n">
+        <v>6914.11</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M71" s="5" t="n">
-        <v>-1</v>
+        <v>5.2382</v>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>5.2382</v>
       </c>
       <c r="N71" t="n">
-        <v>102030.33</v>
+        <v>100000</v>
       </c>
       <c r="O71" t="n">
-        <v>101010.02</v>
+        <v>105238.21</v>
       </c>
     </row>
     <row r="72">
@@ -6603,7 +6589,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -6612,12 +6598,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -6627,27 +6613,30 @@
         <v>6982.4</v>
       </c>
       <c r="H72" t="n">
-        <v>6986.84</v>
+        <v>6988.83</v>
       </c>
       <c r="I72" t="n">
-        <v>6937.52</v>
+        <v>6958.82</v>
+      </c>
+      <c r="J72" t="n">
+        <v>7002</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-1</v>
+        <v>-3.0482</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>-1</v>
+        <v>-3.0482</v>
       </c>
       <c r="N72" t="n">
-        <v>101010.02</v>
+        <v>105238.21</v>
       </c>
       <c r="O72" t="n">
-        <v>99999.92</v>
+        <v>102030.33</v>
       </c>
     </row>
     <row r="73">
@@ -6657,64 +6646,61 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G73" t="n">
-        <v>6794.4</v>
+        <v>6982.4</v>
       </c>
       <c r="H73" t="n">
-        <v>6770.77</v>
+        <v>6992.85</v>
       </c>
       <c r="I73" t="n">
-        <v>6870.44</v>
-      </c>
-      <c r="J73" t="n">
-        <v>6769.03</v>
+        <v>6870.79</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>-1.0736</v>
+        <v>-1</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>-1.0736</v>
+        <v>-1</v>
       </c>
       <c r="N73" t="n">
-        <v>99999.92</v>
+        <v>102030.33</v>
       </c>
       <c r="O73" t="n">
-        <v>98926.28999999999</v>
+        <v>101010.02</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -6723,32 +6709,29 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F74" t="n">
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>86.081</v>
+        <v>6982.4</v>
       </c>
       <c r="H74" t="n">
-        <v>88.001</v>
+        <v>6986.84</v>
       </c>
       <c r="I74" t="n">
-        <v>83.669</v>
-      </c>
-      <c r="J74" t="n">
-        <v>88.001</v>
+        <v>6937.52</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
       <c r="L74" t="n">
@@ -6758,20 +6741,20 @@
         <v>-1</v>
       </c>
       <c r="N74" t="n">
-        <v>100000</v>
+        <v>101010.02</v>
       </c>
       <c r="O74" t="n">
-        <v>99000</v>
+        <v>99999.92</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -6780,51 +6763,51 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>73.84399999999999</v>
+        <v>6794.4</v>
       </c>
       <c r="H75" t="n">
-        <v>71.999</v>
+        <v>6770.77</v>
       </c>
       <c r="I75" t="n">
-        <v>76.301</v>
+        <v>6870.44</v>
       </c>
       <c r="J75" t="n">
-        <v>76.301</v>
+        <v>6769.03</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.3317</v>
-      </c>
-      <c r="M75" s="2" t="n">
-        <v>1.3317</v>
+        <v>-1.0736</v>
+      </c>
+      <c r="M75" s="5" t="n">
+        <v>-1.0736</v>
       </c>
       <c r="N75" t="n">
-        <v>99000</v>
+        <v>99999.92</v>
       </c>
       <c r="O75" t="n">
-        <v>100318.39</v>
+        <v>98926.28999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -6837,108 +6820,108 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>15</v>
+        <v>86.081</v>
       </c>
       <c r="H76" t="n">
-        <v>15.26</v>
+        <v>88.001</v>
       </c>
       <c r="I76" t="n">
-        <v>14.83</v>
+        <v>83.669</v>
       </c>
       <c r="J76" t="n">
-        <v>14.83</v>
+        <v>88.001</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0.6538</v>
-      </c>
-      <c r="M76" s="2" t="n">
-        <v>0.6538</v>
+        <v>-1</v>
+      </c>
+      <c r="M76" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N76" t="n">
         <v>100000</v>
       </c>
       <c r="O76" t="n">
-        <v>100653.85</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F77" t="n">
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>20.89</v>
+        <v>73.84399999999999</v>
       </c>
       <c r="H77" t="n">
-        <v>21.07</v>
+        <v>71.999</v>
       </c>
       <c r="I77" t="n">
-        <v>20.76</v>
+        <v>76.301</v>
       </c>
       <c r="J77" t="n">
-        <v>21.08</v>
+        <v>76.301</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>-1.0556</v>
-      </c>
-      <c r="M77" s="5" t="n">
-        <v>-1.0556</v>
+        <v>1.3317</v>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>1.3317</v>
       </c>
       <c r="N77" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O77" t="n">
-        <v>98944.44</v>
+        <v>100318.39</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -6951,55 +6934,55 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F78" t="n">
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0.8614000000000001</v>
+        <v>15</v>
       </c>
       <c r="H78" t="n">
-        <v>0.8637</v>
+        <v>15.26</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8577</v>
+        <v>14.83</v>
       </c>
       <c r="J78" t="n">
-        <v>0.8637</v>
+        <v>14.83</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M78" s="5" t="n">
-        <v>-1</v>
+        <v>0.6538</v>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>0.6538</v>
       </c>
       <c r="N78" t="n">
         <v>100000</v>
       </c>
       <c r="O78" t="n">
-        <v>99000</v>
+        <v>100653.85</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Teucrium_Wheat_Fund</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -7008,45 +6991,45 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>0.8614000000000001</v>
+        <v>20.89</v>
       </c>
       <c r="H79" t="n">
-        <v>0.8658</v>
+        <v>21.07</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8602</v>
+        <v>20.76</v>
       </c>
       <c r="J79" t="n">
-        <v>0.8602</v>
+        <v>21.08</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0.2727</v>
-      </c>
-      <c r="M79" s="2" t="n">
-        <v>0.2727</v>
+        <v>-1.0556</v>
+      </c>
+      <c r="M79" s="5" t="n">
+        <v>-1.0556</v>
       </c>
       <c r="N79" t="n">
-        <v>99000</v>
+        <v>100000</v>
       </c>
       <c r="O79" t="n">
-        <v>99270</v>
+        <v>98944.44</v>
       </c>
     </row>
     <row r="80">
@@ -7056,64 +7039,64 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>0.8467</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H80" t="n">
-        <v>0.8436</v>
+        <v>0.8637</v>
       </c>
       <c r="I80" t="n">
-        <v>0.85</v>
+        <v>0.8577</v>
       </c>
       <c r="J80" t="n">
-        <v>0.8498</v>
+        <v>0.8637</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>data_end</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1</v>
-      </c>
-      <c r="M80" s="2" t="n">
-        <v>1</v>
+        <v>-1</v>
+      </c>
+      <c r="M80" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N80" t="n">
-        <v>99270</v>
+        <v>100000</v>
       </c>
       <c r="O80" t="n">
-        <v>100262.7</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -7122,108 +7105,108 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>116.5</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H81" t="n">
-        <v>116.79</v>
+        <v>0.8658</v>
       </c>
       <c r="I81" t="n">
-        <v>115.7</v>
+        <v>0.8602</v>
       </c>
       <c r="J81" t="n">
-        <v>116.79</v>
+        <v>0.8602</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M81" s="5" t="n">
-        <v>-1</v>
+        <v>0.2727</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>0.2727</v>
       </c>
       <c r="N81" t="n">
-        <v>100000</v>
+        <v>99000</v>
       </c>
       <c r="O81" t="n">
-        <v>99000</v>
+        <v>99270</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>118.02</v>
+        <v>0.8467</v>
       </c>
       <c r="H82" t="n">
-        <v>118.16</v>
+        <v>0.8436</v>
       </c>
       <c r="I82" t="n">
-        <v>117.17</v>
+        <v>0.85</v>
       </c>
       <c r="J82" t="n">
-        <v>118.16</v>
+        <v>0.8498</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>data_end</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M82" s="5" t="n">
-        <v>-1</v>
+        <v>1</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N82" t="n">
-        <v>99000</v>
+        <v>99270</v>
       </c>
       <c r="O82" t="n">
-        <v>98010</v>
+        <v>100262.7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -7231,56 +7214,56 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F83" t="n">
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>97.81399999999999</v>
+        <v>116.5</v>
       </c>
       <c r="H83" t="n">
-        <v>97.569</v>
+        <v>116.79</v>
       </c>
       <c r="I83" t="n">
-        <v>98.10599999999999</v>
+        <v>115.7</v>
       </c>
       <c r="J83" t="n">
-        <v>98.10599999999999</v>
+        <v>116.79</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.1918</v>
-      </c>
-      <c r="M83" s="2" t="n">
-        <v>1.1918</v>
+        <v>-1</v>
+      </c>
+      <c r="M83" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N83" t="n">
         <v>100000</v>
       </c>
       <c r="O83" t="n">
-        <v>101191.84</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -7288,50 +7271,50 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G84" t="n">
-        <v>97.714</v>
+        <v>118.02</v>
       </c>
       <c r="H84" t="n">
-        <v>97.46899999999999</v>
+        <v>118.16</v>
       </c>
       <c r="I84" t="n">
-        <v>98.211</v>
+        <v>117.17</v>
       </c>
       <c r="J84" t="n">
-        <v>98.211</v>
+        <v>118.16</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.0286</v>
-      </c>
-      <c r="M84" s="2" t="n">
-        <v>2.0286</v>
+        <v>-1</v>
+      </c>
+      <c r="M84" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N84" t="n">
-        <v>101191.84</v>
+        <v>99000</v>
       </c>
       <c r="O84" t="n">
-        <v>103244.59</v>
+        <v>98010</v>
       </c>
     </row>
     <row r="85">
@@ -7341,37 +7324,37 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>99.376</v>
+        <v>97.81399999999999</v>
       </c>
       <c r="H85" t="n">
-        <v>99.571</v>
+        <v>97.569</v>
       </c>
       <c r="I85" t="n">
-        <v>98.874</v>
+        <v>98.10599999999999</v>
       </c>
       <c r="J85" t="n">
-        <v>98.874</v>
+        <v>98.10599999999999</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -7379,16 +7362,16 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.5744</v>
+        <v>1.1918</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2.5744</v>
+        <v>1.1918</v>
       </c>
       <c r="N85" t="n">
-        <v>103244.59</v>
+        <v>100000</v>
       </c>
       <c r="O85" t="n">
-        <v>105902.47</v>
+        <v>101191.84</v>
       </c>
     </row>
     <row r="86">
@@ -7398,54 +7381,54 @@
         </is>
       </c>
       <c r="B86" t="n">
+        <v>2</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
         <v>4</v>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
-        <v>3</v>
-      </c>
       <c r="G86" t="n">
-        <v>99.246</v>
+        <v>97.714</v>
       </c>
       <c r="H86" t="n">
-        <v>99.501</v>
+        <v>97.46899999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>98.849</v>
+        <v>98.211</v>
       </c>
       <c r="J86" t="n">
-        <v>99.501</v>
+        <v>98.211</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M86" s="5" t="n">
-        <v>-1</v>
+        <v>2.0286</v>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>2.0286</v>
       </c>
       <c r="N86" t="n">
-        <v>105902.47</v>
+        <v>101191.84</v>
       </c>
       <c r="O86" t="n">
-        <v>104843.45</v>
+        <v>103244.59</v>
       </c>
     </row>
     <row r="87">
@@ -7455,7 +7438,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -7464,28 +7447,28 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G87" t="n">
-        <v>100.066</v>
+        <v>99.376</v>
       </c>
       <c r="H87" t="n">
-        <v>100.201</v>
+        <v>99.571</v>
       </c>
       <c r="I87" t="n">
-        <v>99.804</v>
+        <v>98.874</v>
       </c>
       <c r="J87" t="n">
-        <v>99.804</v>
+        <v>98.874</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -7493,16 +7476,16 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.9407</v>
+        <v>2.5744</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1.9407</v>
+        <v>2.5744</v>
       </c>
       <c r="N87" t="n">
-        <v>104843.45</v>
+        <v>103244.59</v>
       </c>
       <c r="O87" t="n">
-        <v>106878.19</v>
+        <v>105902.47</v>
       </c>
     </row>
     <row r="88">
@@ -7512,7 +7495,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -7521,45 +7504,45 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G88" t="n">
-        <v>100.066</v>
+        <v>99.246</v>
       </c>
       <c r="H88" t="n">
-        <v>100.316</v>
+        <v>99.501</v>
       </c>
       <c r="I88" t="n">
-        <v>99.56399999999999</v>
+        <v>98.849</v>
       </c>
       <c r="J88" t="n">
-        <v>99.45999999999999</v>
+        <v>99.501</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.424</v>
-      </c>
-      <c r="M88" s="2" t="n">
-        <v>2.424</v>
+        <v>-1</v>
+      </c>
+      <c r="M88" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N88" t="n">
-        <v>106878.19</v>
+        <v>105902.47</v>
       </c>
       <c r="O88" t="n">
-        <v>109468.91</v>
+        <v>104843.45</v>
       </c>
     </row>
     <row r="89">
@@ -7569,7 +7552,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -7578,12 +7561,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -7593,30 +7576,30 @@
         <v>100.066</v>
       </c>
       <c r="H89" t="n">
-        <v>100.361</v>
+        <v>100.201</v>
       </c>
       <c r="I89" t="n">
-        <v>99.249</v>
+        <v>99.804</v>
       </c>
       <c r="J89" t="n">
-        <v>100.361</v>
+        <v>99.804</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M89" s="5" t="n">
-        <v>-1</v>
+        <v>1.9407</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>1.9407</v>
       </c>
       <c r="N89" t="n">
-        <v>109468.91</v>
+        <v>104843.45</v>
       </c>
       <c r="O89" t="n">
-        <v>108374.22</v>
+        <v>106878.19</v>
       </c>
     </row>
     <row r="90">
@@ -7626,7 +7609,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -7635,45 +7618,45 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>100.621</v>
+        <v>100.066</v>
       </c>
       <c r="H90" t="n">
-        <v>100.911</v>
+        <v>100.316</v>
       </c>
       <c r="I90" t="n">
-        <v>100.489</v>
+        <v>99.56399999999999</v>
       </c>
       <c r="J90" t="n">
-        <v>100.911</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M90" s="5" t="n">
-        <v>-1</v>
+        <v>2.424</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>2.424</v>
       </c>
       <c r="N90" t="n">
-        <v>108374.22</v>
+        <v>106878.19</v>
       </c>
       <c r="O90" t="n">
-        <v>107290.48</v>
+        <v>109468.91</v>
       </c>
     </row>
     <row r="91">
@@ -7683,7 +7666,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -7692,45 +7675,45 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F91" t="n">
         <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>101.411</v>
+        <v>100.066</v>
       </c>
       <c r="H91" t="n">
-        <v>101.526</v>
+        <v>100.361</v>
       </c>
       <c r="I91" t="n">
-        <v>101.079</v>
+        <v>99.249</v>
       </c>
       <c r="J91" t="n">
-        <v>101.079</v>
+        <v>100.361</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.887</v>
-      </c>
-      <c r="M91" s="2" t="n">
-        <v>2.887</v>
+        <v>-1</v>
+      </c>
+      <c r="M91" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N91" t="n">
-        <v>107290.48</v>
+        <v>109468.91</v>
       </c>
       <c r="O91" t="n">
-        <v>110387.91</v>
+        <v>108374.22</v>
       </c>
     </row>
     <row r="92">
@@ -7740,7 +7723,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -7749,55 +7732,55 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G92" t="n">
-        <v>101.411</v>
+        <v>100.621</v>
       </c>
       <c r="H92" t="n">
-        <v>101.491</v>
+        <v>100.911</v>
       </c>
       <c r="I92" t="n">
-        <v>101.084</v>
+        <v>100.489</v>
       </c>
       <c r="J92" t="n">
-        <v>101.084</v>
+        <v>100.911</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>target_bar</t>
+          <t>stop</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>4.0875</v>
-      </c>
-      <c r="M92" s="2" t="n">
-        <v>4.0875</v>
+        <v>-1</v>
+      </c>
+      <c r="M92" s="5" t="n">
+        <v>-1</v>
       </c>
       <c r="N92" t="n">
-        <v>110387.91</v>
+        <v>108374.22</v>
       </c>
       <c r="O92" t="n">
-        <v>114900.02</v>
+        <v>107290.48</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -7806,28 +7789,28 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F93" t="n">
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>121.72</v>
+        <v>101.411</v>
       </c>
       <c r="H93" t="n">
-        <v>123.03</v>
+        <v>101.526</v>
       </c>
       <c r="I93" t="n">
-        <v>118.32</v>
+        <v>101.079</v>
       </c>
       <c r="J93" t="n">
-        <v>113.29</v>
+        <v>101.079</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -7835,72 +7818,186 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>6.4351</v>
+        <v>2.887</v>
       </c>
       <c r="M93" s="2" t="n">
-        <v>6.4351</v>
+        <v>2.887</v>
       </c>
       <c r="N93" t="n">
-        <v>100000</v>
+        <v>107290.48</v>
       </c>
       <c r="O93" t="n">
-        <v>106435.11</v>
+        <v>110387.91</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>10</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H94" t="n">
+        <v>101.491</v>
+      </c>
+      <c r="I94" t="n">
+        <v>101.084</v>
+      </c>
+      <c r="J94" t="n">
+        <v>101.084</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>target_bar</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>4.0875</v>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>4.0875</v>
+      </c>
+      <c r="N94" t="n">
+        <v>110387.91</v>
+      </c>
+      <c r="O94" t="n">
+        <v>114900.02</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
           <t>United_States_Oil_Fund_LP</t>
         </is>
       </c>
-      <c r="B94" t="n">
+      <c r="B95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" t="n">
+        <v>121.72</v>
+      </c>
+      <c r="H95" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="I95" t="n">
+        <v>118.32</v>
+      </c>
+      <c r="J95" t="n">
+        <v>113.29</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>target_bar</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>6.4351</v>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>6.4351</v>
+      </c>
+      <c r="N95" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O95" t="n">
+        <v>106435.11</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
         <v>2</v>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>short</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="F94" t="n">
-        <v>1</v>
-      </c>
-      <c r="G94" t="n">
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" t="n">
         <v>130.16</v>
       </c>
-      <c r="H94" t="n">
+      <c r="H96" t="n">
         <v>130.94</v>
       </c>
-      <c r="I94" t="n">
+      <c r="I96" t="n">
         <v>124.19</v>
       </c>
-      <c r="J94" t="n">
+      <c r="J96" t="n">
         <v>124.19</v>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="K96" t="inlineStr">
         <is>
           <t>target_bar</t>
         </is>
       </c>
-      <c r="L94" t="n">
+      <c r="L96" t="n">
         <v>7.6538</v>
       </c>
-      <c r="M94" s="2" t="n">
+      <c r="M96" s="2" t="n">
         <v>7.6538</v>
       </c>
-      <c r="N94" t="n">
+      <c r="N96" t="n">
         <v>106435.11</v>
       </c>
-      <c r="O94" t="n">
+      <c r="O96" t="n">
         <v>114581.49</v>
       </c>
     </row>
